--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2768.67</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>391179.67</v>
+        <v>396731.75</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2764.33</v>
+        <v>2766.75</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>392317.33</v>
+        <v>396961.75</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5533</v>
+        <v>5537.75</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>783497</v>
+        <v>793693.5</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>610</v>
+        <v>608.25</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>118770.67</v>
+        <v>118135.75</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90567.33</v>
+        <v>90399.75</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1222</v>
+        <v>1222.25</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>209338</v>
+        <v>208535.5</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>93.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>92.63</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.7</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>83.68000000000001</v>
+        <v>84.79000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>98.94</v>
+        <v>92.81</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.5</v>
+        <v>82.03</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80.09999999999999</v>
+        <v>81.05</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>88.2</v>
+        <v>85.65000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>80.84999999999999</v>
+        <v>83.20999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>85.66</v>
+        <v>86.52</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H517"/>
+  <dimension ref="A1:H541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21639,6 +21639,966 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>5552</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>5,552</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>824283</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>8,24,283</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>410895</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>4,10,895</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>2774</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2,774</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>413388</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>4,13,388</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>2778</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2,778</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>1223</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>1,223</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>206128</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2,06,128</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>89897</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>89,897</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>620</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>116231</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>1,16,231</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>603</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>86.67</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>86.67%</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>83.43000000000001</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>83.43%</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>85.90%</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>85</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>85.00%</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>90.10%</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>40</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>40.00%</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>87.38%</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>82</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>82.00%</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>85.57%</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>68</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>68.00%</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>83.55%</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21650,7 +22610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22149,6 +23109,31 @@
         <v>80</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C20" t="n">
+        <v>82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>68</v>
+      </c>
+      <c r="F20" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G20" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22160,7 +23145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22672,6 +23657,25 @@
         <v>610</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D27" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E27" t="n">
+        <v>603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2771</v>
+        <v>2752</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>396731.75</v>
+        <v>395357.8</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2766.75</v>
+        <v>2747.6</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396961.75</v>
+        <v>394906</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5537.75</v>
+        <v>5499.6</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793693.5</v>
+        <v>790263.8</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>608.25</v>
+        <v>602.4</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>118135.75</v>
+        <v>116590.2</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>614</v>
+        <v>606.4</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90399.75</v>
+        <v>88509</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1222.25</v>
+        <v>1208.8</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>208535.5</v>
+        <v>205099.2</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>91.59999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.03</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40.85</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>84.79000000000001</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>84</v>
+        <v>79.67</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>92.81</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>82.03</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.05</v>
+        <v>81.17</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>85.65000000000001</v>
+        <v>84.53</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83.20999999999999</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>67.5</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>86.52</v>
+        <v>86.63</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H541"/>
+  <dimension ref="A1:H565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22599,6 +22599,966 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>576</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>579</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>71</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>55</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>82.30%</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22610,7 +23570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23134,6 +24094,31 @@
         <v>83.09999999999999</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>82.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23145,7 +24130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23676,6 +24661,25 @@
         <v>603</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>389862</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2676</v>
+      </c>
+      <c r="D28" t="n">
+        <v>110408</v>
+      </c>
+      <c r="E28" t="n">
+        <v>579</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2746</v>
+        <v>2754.7</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>393427.44</v>
+        <v>397092.2</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2746.11</v>
+        <v>2754.6</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>392905.11</v>
+        <v>396505.3</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5492.11</v>
+        <v>5509.3</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>786332.5600000001</v>
+        <v>793597.5</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>603</v>
+        <v>605.8</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115067</v>
+        <v>115674.8</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>607.4400000000001</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90098.33</v>
+        <v>90951.2</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1210.44</v>
+        <v>1215.8</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>205165.33</v>
+        <v>206626</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>91.89</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86.48</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.99</v>
+        <v>41.42</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.5</v>
+        <v>82.12</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>93.59</v>
+        <v>93.98</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.20999999999999</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80.04000000000001</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80.27</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.09999999999999</v>
+        <v>84.73</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.71</v>
+        <v>60.75</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.23</v>
+        <v>87.61</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H661"/>
+  <dimension ref="A1:H685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19242,12 +19242,12 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -19261,11 +19261,11 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>5613</v>
+        <v>5664</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>5,613</t>
+          <t>5,664</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -19282,12 +19282,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -19301,11 +19301,11 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>846980</v>
+        <v>858982</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>8,46,980</t>
+          <t>8,58,982</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -19322,12 +19322,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -19341,11 +19341,11 @@
         </is>
       </c>
       <c r="E460" t="n">
-        <v>423429</v>
+        <v>428907</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>4,23,429</t>
+          <t>4,28,907</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -19362,12 +19362,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -19381,11 +19381,11 @@
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2803</v>
+        <v>2831</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>2,803</t>
+          <t>2,831</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -19402,12 +19402,12 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -19421,11 +19421,11 @@
         </is>
       </c>
       <c r="E462" t="n">
-        <v>423551</v>
+        <v>430075</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>4,23,551</t>
+          <t>4,30,075</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -19442,12 +19442,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -19461,11 +19461,11 @@
         </is>
       </c>
       <c r="E463" t="n">
-        <v>2810</v>
+        <v>2833</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>2,810</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -19482,12 +19482,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -19501,11 +19501,11 @@
         </is>
       </c>
       <c r="E464" t="n">
-        <v>1222</v>
+        <v>1264</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>1,222</t>
+          <t>1,264</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -19522,12 +19522,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -19541,11 +19541,11 @@
         </is>
       </c>
       <c r="E465" t="n">
-        <v>217278</v>
+        <v>219772</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>2,17,278</t>
+          <t>2,19,772</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -19562,12 +19562,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -19581,11 +19581,11 @@
         </is>
       </c>
       <c r="E466" t="n">
-        <v>99401</v>
+        <v>98627</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>99,401</t>
+          <t>98,627</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -19602,12 +19602,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -19621,11 +19621,11 @@
         </is>
       </c>
       <c r="E467" t="n">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -19642,12 +19642,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -19661,11 +19661,11 @@
         </is>
       </c>
       <c r="E468" t="n">
-        <v>117877</v>
+        <v>121145</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>1,17,877</t>
+          <t>1,21,145</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -19682,12 +19682,12 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -19701,11 +19701,11 @@
         </is>
       </c>
       <c r="E469" t="n">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>631</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -19722,35 +19722,35 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>5687</v>
+        <v>96.67</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>5,687</t>
+          <t>96.67%</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -19762,35 +19762,35 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>859606</v>
+        <v>85.08</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>8,59,606</t>
+          <t>85.08%</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -19802,35 +19802,35 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>427571</v>
+        <v>79.48</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>4,27,571</t>
+          <t>79.48%</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -19842,35 +19842,35 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>2840</v>
+        <v>66</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2,840</t>
+          <t>66.00%</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -19882,35 +19882,35 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>432035</v>
+        <v>94.3</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>4,32,035</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -19922,35 +19922,35 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>2847</v>
+        <v>37.5</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>2,847</t>
+          <t>37.50%</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -19962,35 +19962,35 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>1213</v>
+        <v>90.3</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>1,213</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -20002,35 +20002,35 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>215409</v>
+        <v>86.5</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>2,15,409</t>
+          <t>86.50%</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -20042,35 +20042,35 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>97310</v>
+        <v>89.16</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>97,310</t>
+          <t>89.16%</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -20082,35 +20082,35 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>606</v>
+        <v>61</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>61.00%</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -20122,35 +20122,35 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>118099</v>
+        <v>85.94</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>1,18,099</t>
+          <t>85.94%</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -20162,35 +20162,35 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>607</v>
+        <v>92.8</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>92.80%</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -20202,35 +20202,35 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>95.45</v>
+        <v>5613</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>95.45%</t>
+          <t>5,613</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -20242,35 +20242,35 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>85.93000000000001</v>
+        <v>846980</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>85.93%</t>
+          <t>8,46,980</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -20282,35 +20282,35 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>81.04000000000001</v>
+        <v>423429</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>81.04%</t>
+          <t>4,23,429</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -20322,35 +20322,35 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>78</v>
+        <v>2803</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>78.00%</t>
+          <t>2,803</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -20362,35 +20362,35 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>93</v>
+        <v>423551</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>93.00%</t>
+          <t>4,23,551</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -20402,35 +20402,35 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>45</v>
+        <v>2810</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>2,810</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -20442,35 +20442,35 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>88.51000000000001</v>
+        <v>1222</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>88.51%</t>
+          <t>1,222</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -20482,35 +20482,35 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>83</v>
+        <v>217278</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>83.00%</t>
+          <t>2,17,278</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -20522,35 +20522,35 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>88.86</v>
+        <v>99401</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>88.86%</t>
+          <t>99,401</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -20562,35 +20562,35 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>68</v>
+        <v>604</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>604</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -20602,35 +20602,35 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>84.84999999999999</v>
+        <v>117877</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>84.85%</t>
+          <t>1,17,877</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -20642,35 +20642,35 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>90.3</v>
+        <v>618</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>90.30%</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -20682,12 +20682,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -20701,11 +20701,11 @@
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5528</v>
+        <v>5687</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>5,687</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -20722,12 +20722,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -20741,11 +20741,11 @@
         </is>
       </c>
       <c r="E495" t="n">
-        <v>792412</v>
+        <v>859606</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>7,92,412</t>
+          <t>8,59,606</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -20762,12 +20762,12 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -20781,11 +20781,11 @@
         </is>
       </c>
       <c r="E496" t="n">
-        <v>395038</v>
+        <v>427571</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>3,95,038</t>
+          <t>4,27,571</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -20802,12 +20802,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -20821,11 +20821,11 @@
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2753</v>
+        <v>2840</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,840</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -20842,12 +20842,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -20861,11 +20861,11 @@
         </is>
       </c>
       <c r="E498" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>3,97,374</t>
+          <t>4,32,035</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -20882,12 +20882,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -20901,11 +20901,11 @@
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>2,775</t>
+          <t>2,847</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -20922,12 +20922,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -20941,11 +20941,11 @@
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>1,213</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -20962,12 +20962,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -20981,11 +20981,11 @@
         </is>
       </c>
       <c r="E501" t="n">
-        <v>199997</v>
+        <v>215409</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>1,99,997</t>
+          <t>2,15,409</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -21002,12 +21002,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -21021,11 +21021,11 @@
         </is>
       </c>
       <c r="E502" t="n">
-        <v>89576</v>
+        <v>97310</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>89,576</t>
+          <t>97,310</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -21042,12 +21042,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -21061,11 +21061,11 @@
         </is>
       </c>
       <c r="E503" t="n">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -21082,12 +21082,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -21101,11 +21101,11 @@
         </is>
       </c>
       <c r="E504" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>1,10,421</t>
+          <t>1,18,099</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -21122,12 +21122,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -21141,11 +21141,11 @@
         </is>
       </c>
       <c r="E505" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -21162,12 +21162,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -21181,11 +21181,11 @@
         </is>
       </c>
       <c r="E506" t="n">
-        <v>80.90000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>80.90%</t>
+          <t>95.45%</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -21202,12 +21202,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -21221,11 +21221,11 @@
         </is>
       </c>
       <c r="E507" t="n">
-        <v>72.42</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>72.42%</t>
+          <t>85.93%</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -21242,12 +21242,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -21261,11 +21261,11 @@
         </is>
       </c>
       <c r="E508" t="n">
-        <v>63.55</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>63.55%</t>
+          <t>81.04%</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -21282,12 +21282,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -21301,11 +21301,11 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>78.00%</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -21322,12 +21322,12 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -21341,11 +21341,11 @@
         </is>
       </c>
       <c r="E510" t="n">
-        <v>82.5</v>
+        <v>93</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>82.50%</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -21362,12 +21362,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -21381,11 +21381,11 @@
         </is>
       </c>
       <c r="E511" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>43.80%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -21402,12 +21402,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -21421,11 +21421,11 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>84.47%</t>
+          <t>88.51%</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -21442,12 +21442,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="E513" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -21482,12 +21482,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -21501,11 +21501,11 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>84.98%</t>
+          <t>88.86%</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -21522,12 +21522,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -21541,11 +21541,11 @@
         </is>
       </c>
       <c r="E515" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>65.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -21562,12 +21562,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -21581,11 +21581,11 @@
         </is>
       </c>
       <c r="E516" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>79.10%</t>
+          <t>84.85%</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -21602,12 +21602,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -21621,11 +21621,11 @@
         </is>
       </c>
       <c r="E517" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>80.80%</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -21642,12 +21642,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -21661,11 +21661,11 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5576</v>
+        <v>5528</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -21682,12 +21682,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -21701,11 +21701,11 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>833982</v>
+        <v>792412</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -21722,12 +21722,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -21741,11 +21741,11 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>418396</v>
+        <v>395038</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -21762,12 +21762,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -21781,11 +21781,11 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2788</v>
+        <v>2753</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -21802,12 +21802,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -21821,11 +21821,11 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -21842,12 +21842,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -21861,11 +21861,11 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -21882,12 +21882,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -21901,11 +21901,11 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>1141</v>
+        <v>1183</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -21922,12 +21922,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -21941,11 +21941,11 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>190423</v>
+        <v>199997</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -21962,12 +21962,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -21981,11 +21981,11 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>82129</v>
+        <v>89576</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -22002,12 +22002,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22021,11 +22021,11 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -22042,12 +22042,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22061,11 +22061,11 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -22082,12 +22082,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22101,11 +22101,11 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -22122,12 +22122,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22141,11 +22141,11 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>90.31999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -22162,12 +22162,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22181,11 +22181,11 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>93.51000000000001</v>
+        <v>72.42</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -22202,12 +22202,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22221,11 +22221,11 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>74.27</v>
+        <v>63.55</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -22242,12 +22242,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22261,11 +22261,11 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -22282,12 +22282,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22301,11 +22301,11 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>92.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -22322,12 +22322,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22341,11 +22341,11 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -22362,12 +22362,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22381,11 +22381,11 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -22402,12 +22402,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22442,12 +22442,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22461,11 +22461,11 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -22482,12 +22482,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -22501,11 +22501,11 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -22522,12 +22522,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -22541,11 +22541,11 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -22562,12 +22562,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -22581,11 +22581,11 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>80.80%</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -22602,12 +22602,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -22621,11 +22621,11 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>5685</v>
+        <v>5576</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -22642,12 +22642,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -22661,11 +22661,11 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>838364</v>
+        <v>833982</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -22682,12 +22682,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -22701,11 +22701,11 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>414824</v>
+        <v>418396</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -22722,12 +22722,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -22741,11 +22741,11 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>2833</v>
+        <v>2788</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -22762,12 +22762,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -22781,11 +22781,11 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -22802,12 +22802,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -22821,11 +22821,11 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -22842,12 +22842,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -22861,11 +22861,11 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>1218</v>
+        <v>1141</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -22882,12 +22882,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -22901,11 +22901,11 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>213243</v>
+        <v>190423</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -22922,12 +22922,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -22941,11 +22941,11 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>91058</v>
+        <v>82129</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -22962,12 +22962,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -22981,11 +22981,11 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -23002,12 +23002,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23021,11 +23021,11 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -23042,12 +23042,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23061,11 +23061,11 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -23082,12 +23082,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23101,11 +23101,11 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>89.66</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -23122,12 +23122,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23141,11 +23141,11 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>92.28</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -23162,12 +23162,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23181,11 +23181,11 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>77.13</v>
+        <v>74.27</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -23202,12 +23202,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23221,11 +23221,11 @@
         </is>
       </c>
       <c r="E557" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -23242,12 +23242,12 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23261,11 +23261,11 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -23282,12 +23282,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23301,11 +23301,11 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>41.2</v>
+        <v>30.8</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -23322,12 +23322,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23341,11 +23341,11 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -23362,12 +23362,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23381,11 +23381,11 @@
         </is>
       </c>
       <c r="E561" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -23402,12 +23402,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23421,11 +23421,11 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -23442,12 +23442,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -23461,11 +23461,11 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -23482,12 +23482,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -23501,11 +23501,11 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -23522,12 +23522,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -23541,11 +23541,11 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -23562,35 +23562,35 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -23602,35 +23602,35 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -23642,35 +23642,35 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -23682,35 +23682,35 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -23722,35 +23722,35 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -23762,35 +23762,35 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -23802,35 +23802,35 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -23842,35 +23842,35 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -23882,35 +23882,35 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -23922,35 +23922,35 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -23962,35 +23962,35 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -24002,35 +24002,35 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -24042,35 +24042,35 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -24082,35 +24082,35 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -24122,35 +24122,35 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -24162,35 +24162,35 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -24202,35 +24202,35 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -24242,35 +24242,35 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -24282,35 +24282,35 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -24322,35 +24322,35 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -24362,35 +24362,35 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -24402,35 +24402,35 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -24442,35 +24442,35 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -24482,35 +24482,35 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -24522,35 +24522,35 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -24562,35 +24562,35 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -24602,35 +24602,35 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -24642,35 +24642,35 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -24682,35 +24682,35 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -24722,35 +24722,35 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -24762,35 +24762,35 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -24802,35 +24802,35 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -24842,35 +24842,35 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -24882,35 +24882,35 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -24922,35 +24922,35 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -24962,35 +24962,35 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -25002,12 +25002,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25021,11 +25021,11 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -25042,12 +25042,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25061,11 +25061,11 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -25082,12 +25082,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25101,11 +25101,11 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -25122,12 +25122,12 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25141,11 +25141,11 @@
         </is>
       </c>
       <c r="E605" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -25162,12 +25162,12 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25181,11 +25181,11 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -25202,12 +25202,12 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25221,11 +25221,11 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -25242,12 +25242,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25261,11 +25261,11 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -25282,12 +25282,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -25301,11 +25301,11 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -25322,12 +25322,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -25341,11 +25341,11 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -25362,12 +25362,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -25381,11 +25381,11 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -25402,12 +25402,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -25421,11 +25421,11 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -25442,12 +25442,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -25461,11 +25461,11 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -25482,12 +25482,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -25501,11 +25501,11 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -25522,12 +25522,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -25541,11 +25541,11 @@
         </is>
       </c>
       <c r="E615" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -25562,12 +25562,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -25581,11 +25581,11 @@
         </is>
       </c>
       <c r="E616" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -25602,12 +25602,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -25621,11 +25621,11 @@
         </is>
       </c>
       <c r="E617" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -25642,12 +25642,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -25661,11 +25661,11 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -25682,12 +25682,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -25701,11 +25701,11 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -25722,12 +25722,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -25741,11 +25741,11 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -25762,12 +25762,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -25781,11 +25781,11 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -25802,12 +25802,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -25821,11 +25821,11 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -25842,12 +25842,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -25861,11 +25861,11 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -25882,12 +25882,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -25901,11 +25901,11 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -25922,12 +25922,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -25941,11 +25941,11 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -25962,35 +25962,35 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -26002,35 +26002,35 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -26042,35 +26042,35 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -26082,35 +26082,35 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -26122,35 +26122,35 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -26162,35 +26162,35 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -26202,35 +26202,35 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -26242,35 +26242,35 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -26282,35 +26282,35 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -26322,35 +26322,35 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -26362,35 +26362,35 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -26402,35 +26402,35 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -26442,12 +26442,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -26461,11 +26461,11 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -26482,12 +26482,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -26501,11 +26501,11 @@
         </is>
       </c>
       <c r="E639" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -26522,12 +26522,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -26541,11 +26541,11 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -26562,12 +26562,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -26581,11 +26581,11 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -26602,12 +26602,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -26621,11 +26621,11 @@
         </is>
       </c>
       <c r="E642" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -26642,12 +26642,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -26661,11 +26661,11 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -26682,12 +26682,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -26701,11 +26701,11 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -26722,12 +26722,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -26741,11 +26741,11 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -26762,12 +26762,12 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -26781,11 +26781,11 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -26802,12 +26802,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -26821,11 +26821,11 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -26842,12 +26842,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -26861,11 +26861,11 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -26882,12 +26882,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -26901,11 +26901,11 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -26922,12 +26922,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -26941,11 +26941,11 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -26962,12 +26962,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -26981,11 +26981,11 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -27002,12 +27002,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27021,11 +27021,11 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -27042,12 +27042,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27061,11 +27061,11 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -27082,12 +27082,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27101,11 +27101,11 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -27122,12 +27122,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27141,11 +27141,11 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -27162,12 +27162,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27181,11 +27181,11 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -27202,12 +27202,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27221,11 +27221,11 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -27242,12 +27242,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -27261,11 +27261,11 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -27282,12 +27282,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -27301,11 +27301,11 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -27322,12 +27322,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -27341,11 +27341,11 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -27362,38 +27362,998 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>576</v>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>579</v>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>71</v>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>55</v>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E661" t="n">
+      <c r="E685" t="n">
         <v>82.3</v>
       </c>
-      <c r="F661" t="inlineStr">
+      <c r="F685" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H661" t="inlineStr">
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -27410,7 +28370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -27887,175 +28847,200 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.51000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="C19" t="n">
-        <v>83</v>
+        <v>86.5</v>
       </c>
       <c r="D19" t="n">
-        <v>88.86</v>
+        <v>89.16</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F19" t="n">
-        <v>84.84999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="G19" t="n">
-        <v>90.3</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="D20" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="C21" t="n">
         <v>81.5</v>
       </c>
       <c r="D21" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="E21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C22" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D22" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F22" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G22" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C23" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D23" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F23" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C24" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D24" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G24" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C25" t="n">
+        <v>82</v>
+      </c>
+      <c r="D25" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>68</v>
+      </c>
+      <c r="F25" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G25" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>85.34</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>55</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -28070,7 +29055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -28509,190 +29494,209 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>20 September 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>423551</v>
+        <v>430075</v>
       </c>
       <c r="C23" t="n">
-        <v>2810</v>
+        <v>2833</v>
       </c>
       <c r="D23" t="n">
-        <v>117877</v>
+        <v>121145</v>
       </c>
       <c r="E23" t="n">
-        <v>618</v>
+        <v>631</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>432035</v>
+        <v>423551</v>
       </c>
       <c r="C24" t="n">
-        <v>2847</v>
+        <v>2810</v>
       </c>
       <c r="D24" t="n">
-        <v>118099</v>
+        <v>117877</v>
       </c>
       <c r="E24" t="n">
-        <v>607</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="C25" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="D25" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="E25" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="C26" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="D26" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="E26" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="C27" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="D27" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="E27" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C28" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D28" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E28" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C29" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D29" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E29" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C30" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D30" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E30" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C31" t="n">
         <v>2778</v>
       </c>
       <c r="D31" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E31" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D32" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E32" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" t="n">
         <v>389862</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C33" t="n">
         <v>2676</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D33" t="n">
         <v>110408</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -428,7 +428,7 @@
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2754.7</v>
+        <v>2755.82</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397092.2</v>
+        <v>397851</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2754.6</v>
+        <v>2755.18</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396505.3</v>
+        <v>397585.82</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5509.3</v>
+        <v>5511</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793597.5</v>
+        <v>795436.8199999999</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>605.8</v>
+        <v>605.8200000000001</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115674.8</v>
+        <v>115389.82</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>610</v>
+        <v>611.27</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90951.2</v>
+        <v>91201.09</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1215.8</v>
+        <v>1217.09</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206626</v>
+        <v>206590.91</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.19</v>
+        <v>92.42</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86.3</v>
+        <v>87.08</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.42</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.12</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74.75</v>
+        <v>73.11</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>93.98</v>
+        <v>94.39</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.93000000000001</v>
+        <v>80.95</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80.84999999999999</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>81.84</v>
+        <v>82.13</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.73</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.75</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.61</v>
+        <v>87.78</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H685"/>
+  <dimension ref="A1:H709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -20202,12 +20202,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -20221,11 +20221,11 @@
         </is>
       </c>
       <c r="E482" t="n">
-        <v>5613</v>
+        <v>5528</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>5,613</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -20242,12 +20242,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -20261,11 +20261,11 @@
         </is>
       </c>
       <c r="E483" t="n">
-        <v>846980</v>
+        <v>813830</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>8,46,980</t>
+          <t>8,13,830</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -20282,12 +20282,12 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -20301,11 +20301,11 @@
         </is>
       </c>
       <c r="E484" t="n">
-        <v>423429</v>
+        <v>408391</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>4,23,429</t>
+          <t>4,08,391</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -20322,12 +20322,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -20341,11 +20341,11 @@
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2803</v>
+        <v>2761</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>2,803</t>
+          <t>2,761</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -20362,12 +20362,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -20381,11 +20381,11 @@
         </is>
       </c>
       <c r="E486" t="n">
-        <v>423551</v>
+        <v>405439</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>4,23,551</t>
+          <t>4,05,439</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -20402,12 +20402,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -20421,11 +20421,11 @@
         </is>
       </c>
       <c r="E487" t="n">
-        <v>2810</v>
+        <v>2767</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2,810</t>
+          <t>2,767</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -20442,12 +20442,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -20461,11 +20461,11 @@
         </is>
       </c>
       <c r="E488" t="n">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>1,222</t>
+          <t>1,230</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -20482,12 +20482,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -20501,11 +20501,11 @@
         </is>
       </c>
       <c r="E489" t="n">
-        <v>217278</v>
+        <v>206240</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>2,17,278</t>
+          <t>2,06,240</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -20522,12 +20522,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -20541,11 +20541,11 @@
         </is>
       </c>
       <c r="E490" t="n">
-        <v>99401</v>
+        <v>93700</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>99,401</t>
+          <t>93,700</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -20562,12 +20562,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -20581,11 +20581,11 @@
         </is>
       </c>
       <c r="E491" t="n">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>624</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -20602,12 +20602,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -20621,11 +20621,11 @@
         </is>
       </c>
       <c r="E492" t="n">
-        <v>117877</v>
+        <v>112540</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>1,17,877</t>
+          <t>1,12,540</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -20642,12 +20642,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -20661,11 +20661,11 @@
         </is>
       </c>
       <c r="E493" t="n">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -20682,35 +20682,35 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>5687</v>
+        <v>97.7</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>5,687</t>
+          <t>97.70%</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -20722,35 +20722,35 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>859606</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>8,59,606</t>
+          <t>93.29%</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -20762,35 +20762,35 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>427571</v>
+        <v>74.78</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>4,27,571</t>
+          <t>74.78%</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -20802,35 +20802,35 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2840</v>
+        <v>60</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2,840</t>
+          <t>60.00%</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -20842,35 +20842,35 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>432035</v>
+        <v>94.3</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>4,32,035</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -20882,35 +20882,35 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2847</v>
+        <v>41.7</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>2,847</t>
+          <t>41.70%</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -20922,35 +20922,35 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1213</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>1,213</t>
+          <t>89.15%</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -20962,35 +20962,35 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>215409</v>
+        <v>82.8</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>2,15,409</t>
+          <t>82.80%</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -21002,35 +21002,35 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>97310</v>
+        <v>86.81</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>97,310</t>
+          <t>86.81%</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -21042,35 +21042,35 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>606</v>
+        <v>67</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>67.00%</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -21082,35 +21082,35 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>118099</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>1,18,099</t>
+          <t>81.10%</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -21122,35 +21122,35 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>607</v>
+        <v>84.5</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>84.50%</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -21162,35 +21162,35 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>95.45</v>
+        <v>5613</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>95.45%</t>
+          <t>5,613</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -21202,35 +21202,35 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>85.93000000000001</v>
+        <v>846980</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>85.93%</t>
+          <t>8,46,980</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -21242,35 +21242,35 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>81.04000000000001</v>
+        <v>423429</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>81.04%</t>
+          <t>4,23,429</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -21282,35 +21282,35 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>78</v>
+        <v>2803</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>78.00%</t>
+          <t>2,803</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -21322,35 +21322,35 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>93</v>
+        <v>423551</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>93.00%</t>
+          <t>4,23,551</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -21362,35 +21362,35 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>45</v>
+        <v>2810</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>2,810</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -21402,35 +21402,35 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>88.51000000000001</v>
+        <v>1222</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>88.51%</t>
+          <t>1,222</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -21442,35 +21442,35 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>83</v>
+        <v>217278</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>83.00%</t>
+          <t>2,17,278</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -21482,35 +21482,35 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>88.86</v>
+        <v>99401</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>88.86%</t>
+          <t>99,401</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -21522,35 +21522,35 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>68</v>
+        <v>604</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>604</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -21562,35 +21562,35 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>84.84999999999999</v>
+        <v>117877</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>84.85%</t>
+          <t>1,17,877</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
@@ -21602,35 +21602,35 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>90.3</v>
+        <v>618</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>90.30%</t>
+          <t>618</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -21642,12 +21642,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -21661,11 +21661,11 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5528</v>
+        <v>5687</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>5,687</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -21682,12 +21682,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -21701,11 +21701,11 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>792412</v>
+        <v>859606</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>7,92,412</t>
+          <t>8,59,606</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -21722,12 +21722,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -21741,11 +21741,11 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>395038</v>
+        <v>427571</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>3,95,038</t>
+          <t>4,27,571</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -21762,12 +21762,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -21781,11 +21781,11 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2753</v>
+        <v>2840</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,840</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -21802,12 +21802,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -21821,11 +21821,11 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>3,97,374</t>
+          <t>4,32,035</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -21842,12 +21842,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -21861,11 +21861,11 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2,775</t>
+          <t>2,847</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -21882,12 +21882,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -21901,11 +21901,11 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>1,213</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -21922,12 +21922,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -21941,11 +21941,11 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>199997</v>
+        <v>215409</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>1,99,997</t>
+          <t>2,15,409</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -21962,12 +21962,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -21981,11 +21981,11 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>89576</v>
+        <v>97310</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>89,576</t>
+          <t>97,310</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -22002,12 +22002,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22021,11 +22021,11 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -22042,12 +22042,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22061,11 +22061,11 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>1,10,421</t>
+          <t>1,18,099</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -22082,12 +22082,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22101,11 +22101,11 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -22122,12 +22122,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22141,11 +22141,11 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>80.90000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>80.90%</t>
+          <t>95.45%</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -22162,12 +22162,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22181,11 +22181,11 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>72.42</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>72.42%</t>
+          <t>85.93%</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -22202,12 +22202,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22221,11 +22221,11 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>63.55</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>63.55%</t>
+          <t>81.04%</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -22242,12 +22242,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22261,11 +22261,11 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>78.00%</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -22282,12 +22282,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22301,11 +22301,11 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>82.5</v>
+        <v>93</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>82.50%</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -22322,12 +22322,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22341,11 +22341,11 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>43.80%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -22362,12 +22362,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22381,11 +22381,11 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>84.47%</t>
+          <t>88.51%</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -22402,12 +22402,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22421,11 +22421,11 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -22442,12 +22442,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22461,11 +22461,11 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>84.98%</t>
+          <t>88.86%</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -22482,12 +22482,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -22501,11 +22501,11 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>65.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -22522,12 +22522,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -22541,11 +22541,11 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>79.10%</t>
+          <t>84.85%</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -22562,12 +22562,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -22581,11 +22581,11 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>80.80%</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -22602,12 +22602,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -22621,11 +22621,11 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>5576</v>
+        <v>5528</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -22642,12 +22642,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -22661,11 +22661,11 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>833982</v>
+        <v>792412</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -22682,12 +22682,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -22701,11 +22701,11 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>418396</v>
+        <v>395038</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -22722,12 +22722,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -22741,11 +22741,11 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>2788</v>
+        <v>2753</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -22762,12 +22762,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -22781,11 +22781,11 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -22802,12 +22802,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -22821,11 +22821,11 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -22842,12 +22842,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -22861,11 +22861,11 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>1141</v>
+        <v>1183</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -22882,12 +22882,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -22901,11 +22901,11 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>190423</v>
+        <v>199997</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -22922,12 +22922,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -22941,11 +22941,11 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>82129</v>
+        <v>89576</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -22962,12 +22962,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -22981,11 +22981,11 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -23002,12 +23002,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23021,11 +23021,11 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -23042,12 +23042,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23061,11 +23061,11 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -23082,12 +23082,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23101,11 +23101,11 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>90.31999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -23122,12 +23122,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23141,11 +23141,11 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>93.51000000000001</v>
+        <v>72.42</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -23162,12 +23162,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23181,11 +23181,11 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>74.27</v>
+        <v>63.55</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -23202,12 +23202,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23221,11 +23221,11 @@
         </is>
       </c>
       <c r="E557" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -23242,12 +23242,12 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23261,11 +23261,11 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>92.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -23282,12 +23282,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23301,11 +23301,11 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -23322,12 +23322,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23341,11 +23341,11 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -23362,12 +23362,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23402,12 +23402,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23421,11 +23421,11 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -23442,12 +23442,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -23461,11 +23461,11 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -23482,12 +23482,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -23501,11 +23501,11 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -23522,12 +23522,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -23541,11 +23541,11 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>80.80%</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -23562,12 +23562,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -23581,11 +23581,11 @@
         </is>
       </c>
       <c r="E566" t="n">
-        <v>5685</v>
+        <v>5576</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -23602,12 +23602,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -23621,11 +23621,11 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>838364</v>
+        <v>833982</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -23642,12 +23642,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -23661,11 +23661,11 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>414824</v>
+        <v>418396</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -23682,12 +23682,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -23701,11 +23701,11 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>2833</v>
+        <v>2788</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -23722,12 +23722,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -23741,11 +23741,11 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -23762,12 +23762,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -23781,11 +23781,11 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -23802,12 +23802,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -23821,11 +23821,11 @@
         </is>
       </c>
       <c r="E572" t="n">
-        <v>1218</v>
+        <v>1141</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -23842,12 +23842,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -23861,11 +23861,11 @@
         </is>
       </c>
       <c r="E573" t="n">
-        <v>213243</v>
+        <v>190423</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -23882,12 +23882,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -23901,11 +23901,11 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>91058</v>
+        <v>82129</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -23922,12 +23922,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -23941,11 +23941,11 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -23962,12 +23962,12 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -23981,11 +23981,11 @@
         </is>
       </c>
       <c r="E576" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -24002,12 +24002,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24021,11 +24021,11 @@
         </is>
       </c>
       <c r="E577" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -24042,12 +24042,12 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24061,11 +24061,11 @@
         </is>
       </c>
       <c r="E578" t="n">
-        <v>89.66</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -24082,12 +24082,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24101,11 +24101,11 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>92.28</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -24122,12 +24122,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24141,11 +24141,11 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>77.13</v>
+        <v>74.27</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -24162,12 +24162,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24181,11 +24181,11 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -24202,12 +24202,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24221,11 +24221,11 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -24242,12 +24242,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24261,11 +24261,11 @@
         </is>
       </c>
       <c r="E583" t="n">
-        <v>41.2</v>
+        <v>30.8</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -24282,12 +24282,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24301,11 +24301,11 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -24322,12 +24322,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24341,11 +24341,11 @@
         </is>
       </c>
       <c r="E585" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
@@ -24362,12 +24362,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -24381,11 +24381,11 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -24402,12 +24402,12 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -24421,11 +24421,11 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -24442,12 +24442,12 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -24461,11 +24461,11 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -24482,12 +24482,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -24501,11 +24501,11 @@
         </is>
       </c>
       <c r="E589" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
@@ -24522,35 +24522,35 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -24562,35 +24562,35 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -24602,35 +24602,35 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -24642,35 +24642,35 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -24682,35 +24682,35 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -24722,35 +24722,35 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -24762,35 +24762,35 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -24802,35 +24802,35 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -24842,35 +24842,35 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -24882,35 +24882,35 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -24922,35 +24922,35 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -24962,35 +24962,35 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -25002,35 +25002,35 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -25042,35 +25042,35 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -25082,35 +25082,35 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -25122,35 +25122,35 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -25162,35 +25162,35 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -25202,35 +25202,35 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -25242,35 +25242,35 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -25282,35 +25282,35 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -25322,35 +25322,35 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -25362,35 +25362,35 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -25402,35 +25402,35 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -25442,35 +25442,35 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -25482,35 +25482,35 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -25522,35 +25522,35 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -25562,35 +25562,35 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -25602,35 +25602,35 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -25642,35 +25642,35 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -25682,35 +25682,35 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -25722,35 +25722,35 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -25762,35 +25762,35 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -25802,35 +25802,35 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -25842,35 +25842,35 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -25882,35 +25882,35 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -25922,35 +25922,35 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -25962,12 +25962,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -25981,11 +25981,11 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -26002,12 +26002,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26021,11 +26021,11 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -26042,12 +26042,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26061,11 +26061,11 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -26082,12 +26082,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26101,11 +26101,11 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -26122,12 +26122,12 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26141,11 +26141,11 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -26162,12 +26162,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26181,11 +26181,11 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -26202,12 +26202,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26221,11 +26221,11 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -26242,12 +26242,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -26261,11 +26261,11 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -26282,12 +26282,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -26301,11 +26301,11 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -26322,12 +26322,12 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -26341,11 +26341,11 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -26362,12 +26362,12 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -26381,11 +26381,11 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -26402,12 +26402,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -26421,11 +26421,11 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -26442,12 +26442,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -26461,11 +26461,11 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -26482,12 +26482,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -26501,11 +26501,11 @@
         </is>
       </c>
       <c r="E639" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -26522,12 +26522,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -26541,11 +26541,11 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -26562,12 +26562,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -26581,11 +26581,11 @@
         </is>
       </c>
       <c r="E641" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -26602,12 +26602,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -26621,11 +26621,11 @@
         </is>
       </c>
       <c r="E642" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -26642,12 +26642,12 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -26661,11 +26661,11 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -26682,12 +26682,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -26701,11 +26701,11 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -26722,12 +26722,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -26741,11 +26741,11 @@
         </is>
       </c>
       <c r="E645" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -26762,12 +26762,12 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -26781,11 +26781,11 @@
         </is>
       </c>
       <c r="E646" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -26802,12 +26802,12 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -26821,11 +26821,11 @@
         </is>
       </c>
       <c r="E647" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -26842,12 +26842,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -26861,11 +26861,11 @@
         </is>
       </c>
       <c r="E648" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -26882,12 +26882,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -26901,11 +26901,11 @@
         </is>
       </c>
       <c r="E649" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -26922,35 +26922,35 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -26962,35 +26962,35 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -27002,35 +27002,35 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -27042,35 +27042,35 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -27082,35 +27082,35 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -27122,35 +27122,35 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -27162,35 +27162,35 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -27202,35 +27202,35 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -27242,35 +27242,35 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -27282,35 +27282,35 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -27322,35 +27322,35 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -27362,35 +27362,35 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -27402,12 +27402,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -27421,11 +27421,11 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -27442,12 +27442,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -27461,11 +27461,11 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -27482,12 +27482,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -27501,11 +27501,11 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -27522,12 +27522,12 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -27541,11 +27541,11 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -27562,12 +27562,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -27581,11 +27581,11 @@
         </is>
       </c>
       <c r="E666" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -27602,12 +27602,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -27621,11 +27621,11 @@
         </is>
       </c>
       <c r="E667" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -27642,12 +27642,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -27661,11 +27661,11 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -27682,12 +27682,12 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -27701,11 +27701,11 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -27722,12 +27722,12 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -27741,11 +27741,11 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -27762,12 +27762,12 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -27781,11 +27781,11 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -27802,12 +27802,12 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -27821,11 +27821,11 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -27842,12 +27842,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -27861,11 +27861,11 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -27882,12 +27882,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -27901,11 +27901,11 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -27922,12 +27922,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -27941,11 +27941,11 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -27962,12 +27962,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -27981,11 +27981,11 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -28002,12 +28002,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28021,11 +28021,11 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -28042,12 +28042,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28061,11 +28061,11 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -28082,12 +28082,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28101,11 +28101,11 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -28122,12 +28122,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28141,11 +28141,11 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -28162,12 +28162,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28181,11 +28181,11 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -28202,12 +28202,12 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -28221,11 +28221,11 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -28242,12 +28242,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -28261,11 +28261,11 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -28282,12 +28282,12 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -28301,11 +28301,11 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -28322,38 +28322,998 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
+      <c r="B686" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C685" t="inlineStr">
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>576</v>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>579</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>71</v>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr">
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>55</v>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E685" t="n">
+      <c r="E709" t="n">
         <v>82.3</v>
       </c>
-      <c r="F685" t="inlineStr">
+      <c r="F709" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G685" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H685" t="inlineStr">
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -28370,7 +29330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -28872,175 +29832,200 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88.51000000000001</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>83</v>
+        <v>82.8</v>
       </c>
       <c r="D20" t="n">
-        <v>88.86</v>
+        <v>86.81</v>
       </c>
       <c r="E20" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20" t="n">
-        <v>84.84999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>90.3</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="C22" t="n">
         <v>81.5</v>
       </c>
       <c r="D22" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="E22" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F22" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C23" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D23" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E23" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F23" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G23" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C24" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D24" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C25" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D25" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G25" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C26" t="n">
+        <v>82</v>
+      </c>
+      <c r="D26" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>68</v>
+      </c>
+      <c r="F26" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G26" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D27" t="n">
         <v>85.34</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>55</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -29055,7 +30040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -29513,190 +30498,209 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>21 September 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>423551</v>
+        <v>405439</v>
       </c>
       <c r="C24" t="n">
-        <v>2810</v>
+        <v>2767</v>
       </c>
       <c r="D24" t="n">
-        <v>117877</v>
+        <v>112540</v>
       </c>
       <c r="E24" t="n">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 August 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>432035</v>
+        <v>423551</v>
       </c>
       <c r="C25" t="n">
-        <v>2847</v>
+        <v>2810</v>
       </c>
       <c r="D25" t="n">
-        <v>118099</v>
+        <v>117877</v>
       </c>
       <c r="E25" t="n">
-        <v>607</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="C26" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="D26" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="E26" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="C27" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="D27" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="E27" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="C28" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="D28" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="E28" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C29" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D29" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E29" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C30" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D30" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E30" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C31" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D31" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E31" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C32" t="n">
         <v>2778</v>
       </c>
       <c r="D32" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E32" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D33" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E33" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B34" t="n">
         <v>389862</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>2676</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D34" t="n">
         <v>110408</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E34" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2755.82</v>
+        <v>2746.92</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397851</v>
+        <v>396269.25</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2755.18</v>
+        <v>2746.75</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>397585.82</v>
+        <v>396306.25</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5511</v>
+        <v>5493.67</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>795436.8199999999</v>
+        <v>792575.5</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>605.8200000000001</v>
+        <v>603.42</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>115389.82</v>
+        <v>114515.58</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>611.27</v>
+        <v>607.67</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>91201.09</v>
+        <v>90100.75</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1217.09</v>
+        <v>1211.08</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>206590.91</v>
+        <v>204616.33</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.42</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.08</v>
+        <v>87.66</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>41.46</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>81.3</v>
+        <v>82.34</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>73.11</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.39</v>
+        <v>94.84</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.95</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.06999999999999</v>
+        <v>81.09</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.13</v>
+        <v>82.31999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>84.95999999999999</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.44</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.78</v>
+        <v>87.34</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H709"/>
+  <dimension ref="A1:H733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21642,12 +21642,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -21661,11 +21661,11 @@
         </is>
       </c>
       <c r="E518" t="n">
-        <v>5687</v>
+        <v>5303</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>5,687</t>
+          <t>5,303</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -21682,12 +21682,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -21701,11 +21701,11 @@
         </is>
       </c>
       <c r="E519" t="n">
-        <v>859606</v>
+        <v>761101</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>8,59,606</t>
+          <t>7,61,101</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -21722,12 +21722,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -21741,11 +21741,11 @@
         </is>
       </c>
       <c r="E520" t="n">
-        <v>427571</v>
+        <v>382231</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>4,27,571</t>
+          <t>3,82,231</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -21762,12 +21762,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -21781,11 +21781,11 @@
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2840</v>
+        <v>2654</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>2,840</t>
+          <t>2,654</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -21802,12 +21802,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -21821,11 +21821,11 @@
         </is>
       </c>
       <c r="E522" t="n">
-        <v>432035</v>
+        <v>378870</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>4,32,035</t>
+          <t>3,78,870</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -21842,12 +21842,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -21861,11 +21861,11 @@
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2847</v>
+        <v>2649</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2,847</t>
+          <t>2,649</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -21882,12 +21882,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -21901,11 +21901,11 @@
         </is>
       </c>
       <c r="E524" t="n">
-        <v>1213</v>
+        <v>1145</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>1,213</t>
+          <t>1,145</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -21922,12 +21922,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -21941,11 +21941,11 @@
         </is>
       </c>
       <c r="E525" t="n">
-        <v>215409</v>
+        <v>182896</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>2,15,409</t>
+          <t>1,82,896</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -21962,12 +21962,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -21981,11 +21981,11 @@
         </is>
       </c>
       <c r="E526" t="n">
-        <v>97310</v>
+        <v>77997</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>97,310</t>
+          <t>77,997</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -22002,12 +22002,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -22021,11 +22021,11 @@
         </is>
       </c>
       <c r="E527" t="n">
-        <v>606</v>
+        <v>568</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>568</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -22042,12 +22042,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -22061,11 +22061,11 @@
         </is>
       </c>
       <c r="E528" t="n">
-        <v>118099</v>
+        <v>104899</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>1,18,099</t>
+          <t>1,04,899</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -22082,12 +22082,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -22101,11 +22101,11 @@
         </is>
       </c>
       <c r="E529" t="n">
-        <v>607</v>
+        <v>577</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>577</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -22122,12 +22122,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -22141,11 +22141,11 @@
         </is>
       </c>
       <c r="E530" t="n">
-        <v>95.45</v>
+        <v>98.86</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>95.45%</t>
+          <t>98.86%</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -22162,12 +22162,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -22181,11 +22181,11 @@
         </is>
       </c>
       <c r="E531" t="n">
-        <v>85.93000000000001</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>85.93%</t>
+          <t>92.93%</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -22202,12 +22202,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -22221,11 +22221,11 @@
         </is>
       </c>
       <c r="E532" t="n">
-        <v>81.04000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>81.04%</t>
+          <t>91.63%</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -22242,12 +22242,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -22261,11 +22261,11 @@
         </is>
       </c>
       <c r="E533" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>78.00%</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -22282,12 +22282,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -22301,11 +22301,11 @@
         </is>
       </c>
       <c r="E534" t="n">
-        <v>93</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>93.00%</t>
+          <t>94.60%</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -22322,12 +22322,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -22341,11 +22341,11 @@
         </is>
       </c>
       <c r="E535" t="n">
-        <v>45</v>
+        <v>26.7</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>26.70%</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -22362,12 +22362,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -22381,11 +22381,11 @@
         </is>
       </c>
       <c r="E536" t="n">
-        <v>88.51000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>88.51%</t>
+          <t>83.33%</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -22402,12 +22402,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -22421,11 +22421,11 @@
         </is>
       </c>
       <c r="E537" t="n">
-        <v>83</v>
+        <v>81.3</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>83.00%</t>
+          <t>81.30%</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -22442,12 +22442,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -22461,11 +22461,11 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>88.86</v>
+        <v>85.38</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>88.86%</t>
+          <t>85.38%</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -22482,12 +22482,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -22501,11 +22501,11 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>53.00%</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -22522,12 +22522,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -22541,11 +22541,11 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>84.84999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>84.85%</t>
+          <t>79.50%</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -22562,12 +22562,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -22581,11 +22581,11 @@
         </is>
       </c>
       <c r="E541" t="n">
-        <v>90.3</v>
+        <v>84</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>90.30%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -22602,12 +22602,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -22621,11 +22621,11 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>5528</v>
+        <v>5687</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>5,687</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -22642,12 +22642,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -22661,11 +22661,11 @@
         </is>
       </c>
       <c r="E543" t="n">
-        <v>792412</v>
+        <v>859606</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>7,92,412</t>
+          <t>8,59,606</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -22682,12 +22682,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -22701,11 +22701,11 @@
         </is>
       </c>
       <c r="E544" t="n">
-        <v>395038</v>
+        <v>427571</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>3,95,038</t>
+          <t>4,27,571</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -22722,12 +22722,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -22741,11 +22741,11 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>2753</v>
+        <v>2840</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,840</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -22762,12 +22762,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -22781,11 +22781,11 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>3,97,374</t>
+          <t>4,32,035</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -22802,12 +22802,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -22821,11 +22821,11 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>2,775</t>
+          <t>2,847</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -22842,12 +22842,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -22861,11 +22861,11 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>1183</v>
+        <v>1213</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>1,213</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -22882,12 +22882,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -22901,11 +22901,11 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>199997</v>
+        <v>215409</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>1,99,997</t>
+          <t>2,15,409</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -22922,12 +22922,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -22941,11 +22941,11 @@
         </is>
       </c>
       <c r="E550" t="n">
-        <v>89576</v>
+        <v>97310</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>89,576</t>
+          <t>97,310</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -22962,12 +22962,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -22981,11 +22981,11 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -23002,12 +23002,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -23021,11 +23021,11 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>1,10,421</t>
+          <t>1,18,099</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -23042,12 +23042,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -23061,11 +23061,11 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -23082,12 +23082,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -23101,11 +23101,11 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>80.90000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>80.90%</t>
+          <t>95.45%</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -23122,12 +23122,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -23141,11 +23141,11 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>72.42</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>72.42%</t>
+          <t>85.93%</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -23162,12 +23162,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -23181,11 +23181,11 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>63.55</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>63.55%</t>
+          <t>81.04%</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -23202,12 +23202,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -23221,11 +23221,11 @@
         </is>
       </c>
       <c r="E557" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>78.00%</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -23242,12 +23242,12 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -23261,11 +23261,11 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>82.5</v>
+        <v>93</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>82.50%</t>
+          <t>93.00%</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -23282,12 +23282,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -23301,11 +23301,11 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>43.80%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -23322,12 +23322,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -23341,11 +23341,11 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>84.47%</t>
+          <t>88.51%</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -23362,12 +23362,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -23381,11 +23381,11 @@
         </is>
       </c>
       <c r="E561" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -23402,12 +23402,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -23421,11 +23421,11 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>84.98%</t>
+          <t>88.86%</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -23442,12 +23442,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -23461,11 +23461,11 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>65.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -23482,12 +23482,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -23501,11 +23501,11 @@
         </is>
       </c>
       <c r="E564" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>79.10%</t>
+          <t>84.85%</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -23522,12 +23522,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -23541,11 +23541,11 @@
         </is>
       </c>
       <c r="E565" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>80.80%</t>
+          <t>90.30%</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -23562,12 +23562,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -23581,11 +23581,11 @@
         </is>
       </c>
       <c r="E566" t="n">
-        <v>5576</v>
+        <v>5528</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -23602,12 +23602,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -23621,11 +23621,11 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>833982</v>
+        <v>792412</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -23642,12 +23642,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -23661,11 +23661,11 @@
         </is>
       </c>
       <c r="E568" t="n">
-        <v>418396</v>
+        <v>395038</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -23682,12 +23682,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -23701,11 +23701,11 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>2788</v>
+        <v>2753</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -23722,12 +23722,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -23741,11 +23741,11 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -23762,12 +23762,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -23781,11 +23781,11 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -23802,12 +23802,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -23821,11 +23821,11 @@
         </is>
       </c>
       <c r="E572" t="n">
-        <v>1141</v>
+        <v>1183</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -23842,12 +23842,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -23861,11 +23861,11 @@
         </is>
       </c>
       <c r="E573" t="n">
-        <v>190423</v>
+        <v>199997</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -23882,12 +23882,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -23901,11 +23901,11 @@
         </is>
       </c>
       <c r="E574" t="n">
-        <v>82129</v>
+        <v>89576</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -23922,12 +23922,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -23941,11 +23941,11 @@
         </is>
       </c>
       <c r="E575" t="n">
-        <v>572</v>
+        <v>596</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -23962,12 +23962,12 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -23981,11 +23981,11 @@
         </is>
       </c>
       <c r="E576" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -24002,12 +24002,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -24021,11 +24021,11 @@
         </is>
       </c>
       <c r="E577" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -24042,12 +24042,12 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -24061,11 +24061,11 @@
         </is>
       </c>
       <c r="E578" t="n">
-        <v>90.31999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -24082,12 +24082,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -24101,11 +24101,11 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>93.51000000000001</v>
+        <v>72.42</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -24122,12 +24122,12 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -24141,11 +24141,11 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>74.27</v>
+        <v>63.55</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -24162,12 +24162,12 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -24181,11 +24181,11 @@
         </is>
       </c>
       <c r="E581" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -24202,12 +24202,12 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -24221,11 +24221,11 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>92.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -24242,12 +24242,12 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -24261,11 +24261,11 @@
         </is>
       </c>
       <c r="E583" t="n">
-        <v>30.8</v>
+        <v>43.8</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -24282,12 +24282,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -24301,11 +24301,11 @@
         </is>
       </c>
       <c r="E584" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -24322,12 +24322,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -24362,12 +24362,12 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -24381,11 +24381,11 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -24402,12 +24402,12 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -24421,11 +24421,11 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -24442,12 +24442,12 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -24461,11 +24461,11 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -24482,12 +24482,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -24501,11 +24501,11 @@
         </is>
       </c>
       <c r="E589" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>80.80%</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
@@ -24522,12 +24522,12 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -24541,11 +24541,11 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>5685</v>
+        <v>5576</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -24562,12 +24562,12 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -24581,11 +24581,11 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>838364</v>
+        <v>833982</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -24602,12 +24602,12 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -24621,11 +24621,11 @@
         </is>
       </c>
       <c r="E592" t="n">
-        <v>414824</v>
+        <v>418396</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -24642,12 +24642,12 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -24661,11 +24661,11 @@
         </is>
       </c>
       <c r="E593" t="n">
-        <v>2833</v>
+        <v>2788</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -24682,12 +24682,12 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -24701,11 +24701,11 @@
         </is>
       </c>
       <c r="E594" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -24722,12 +24722,12 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -24741,11 +24741,11 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -24762,12 +24762,12 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -24781,11 +24781,11 @@
         </is>
       </c>
       <c r="E596" t="n">
-        <v>1218</v>
+        <v>1141</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -24802,12 +24802,12 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -24821,11 +24821,11 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>213243</v>
+        <v>190423</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -24842,12 +24842,12 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -24861,11 +24861,11 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>91058</v>
+        <v>82129</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -24882,12 +24882,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -24901,11 +24901,11 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -24922,12 +24922,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -24941,11 +24941,11 @@
         </is>
       </c>
       <c r="E600" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -24962,12 +24962,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -24981,11 +24981,11 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -25002,12 +25002,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -25021,11 +25021,11 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>89.66</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -25042,12 +25042,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -25061,11 +25061,11 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>92.28</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -25082,12 +25082,12 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -25101,11 +25101,11 @@
         </is>
       </c>
       <c r="E604" t="n">
-        <v>77.13</v>
+        <v>74.27</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -25122,12 +25122,12 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -25141,11 +25141,11 @@
         </is>
       </c>
       <c r="E605" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -25162,12 +25162,12 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -25181,11 +25181,11 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -25202,12 +25202,12 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -25221,11 +25221,11 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>41.2</v>
+        <v>30.8</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -25242,12 +25242,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -25261,11 +25261,11 @@
         </is>
       </c>
       <c r="E608" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -25282,12 +25282,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -25301,11 +25301,11 @@
         </is>
       </c>
       <c r="E609" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -25322,12 +25322,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -25341,11 +25341,11 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -25362,12 +25362,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -25381,11 +25381,11 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -25402,12 +25402,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -25421,11 +25421,11 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -25442,12 +25442,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -25461,11 +25461,11 @@
         </is>
       </c>
       <c r="E613" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -25482,35 +25482,35 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -25522,35 +25522,35 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -25562,35 +25562,35 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -25602,35 +25602,35 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -25642,35 +25642,35 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -25682,35 +25682,35 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -25722,35 +25722,35 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -25762,35 +25762,35 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -25802,35 +25802,35 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -25842,35 +25842,35 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -25882,35 +25882,35 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -25922,35 +25922,35 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -25962,35 +25962,35 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -26002,35 +26002,35 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -26042,35 +26042,35 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -26082,35 +26082,35 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -26122,35 +26122,35 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -26162,35 +26162,35 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -26202,35 +26202,35 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -26242,35 +26242,35 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -26282,35 +26282,35 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -26322,35 +26322,35 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -26362,35 +26362,35 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -26402,35 +26402,35 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -26442,35 +26442,35 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -26482,35 +26482,35 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -26522,35 +26522,35 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -26562,35 +26562,35 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -26602,35 +26602,35 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -26642,35 +26642,35 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -26682,35 +26682,35 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -26722,35 +26722,35 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -26762,35 +26762,35 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -26802,35 +26802,35 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -26842,35 +26842,35 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -26882,35 +26882,35 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -26922,12 +26922,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -26941,11 +26941,11 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -26962,12 +26962,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -26981,11 +26981,11 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -27002,12 +27002,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27021,11 +27021,11 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -27042,12 +27042,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27061,11 +27061,11 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -27082,12 +27082,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27101,11 +27101,11 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -27122,12 +27122,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27141,11 +27141,11 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -27162,12 +27162,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27181,11 +27181,11 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -27202,12 +27202,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27221,11 +27221,11 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -27242,12 +27242,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -27261,11 +27261,11 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -27282,12 +27282,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -27301,11 +27301,11 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -27322,12 +27322,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -27341,11 +27341,11 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -27362,12 +27362,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -27381,11 +27381,11 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -27402,12 +27402,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -27421,11 +27421,11 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -27442,12 +27442,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -27461,11 +27461,11 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -27482,12 +27482,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -27501,11 +27501,11 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -27522,12 +27522,12 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -27541,11 +27541,11 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -27562,12 +27562,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -27581,11 +27581,11 @@
         </is>
       </c>
       <c r="E666" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -27602,12 +27602,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -27621,11 +27621,11 @@
         </is>
       </c>
       <c r="E667" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -27642,12 +27642,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -27661,11 +27661,11 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -27682,12 +27682,12 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -27701,11 +27701,11 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -27722,12 +27722,12 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -27741,11 +27741,11 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -27762,12 +27762,12 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -27781,11 +27781,11 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -27802,12 +27802,12 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -27821,11 +27821,11 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -27842,12 +27842,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -27861,11 +27861,11 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -27882,35 +27882,35 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -27922,35 +27922,35 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -27962,35 +27962,35 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -28002,35 +28002,35 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -28042,35 +28042,35 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -28082,35 +28082,35 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -28122,35 +28122,35 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -28162,35 +28162,35 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -28202,35 +28202,35 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -28242,35 +28242,35 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -28282,35 +28282,35 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -28322,35 +28322,35 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -28362,12 +28362,12 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -28381,11 +28381,11 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -28402,12 +28402,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -28421,11 +28421,11 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -28442,12 +28442,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -28461,11 +28461,11 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -28482,12 +28482,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -28501,11 +28501,11 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -28522,12 +28522,12 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -28541,11 +28541,11 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -28562,12 +28562,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -28581,11 +28581,11 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -28602,12 +28602,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -28621,11 +28621,11 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -28642,12 +28642,12 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -28661,11 +28661,11 @@
         </is>
       </c>
       <c r="E693" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -28682,12 +28682,12 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -28701,11 +28701,11 @@
         </is>
       </c>
       <c r="E694" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -28722,12 +28722,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -28741,11 +28741,11 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -28762,12 +28762,12 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -28781,11 +28781,11 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -28802,12 +28802,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -28821,11 +28821,11 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -28842,12 +28842,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -28861,11 +28861,11 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -28882,12 +28882,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -28901,11 +28901,11 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -28922,12 +28922,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -28941,11 +28941,11 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -28962,12 +28962,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -28981,11 +28981,11 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29021,11 +29021,11 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -29042,12 +29042,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29061,11 +29061,11 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -29082,12 +29082,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29101,11 +29101,11 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -29122,12 +29122,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29141,11 +29141,11 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -29162,12 +29162,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -29181,11 +29181,11 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -29202,12 +29202,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -29221,11 +29221,11 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -29242,12 +29242,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -29261,11 +29261,11 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -29282,38 +29282,998 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B709" t="inlineStr">
+      <c r="B710" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C709" t="inlineStr">
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>576</v>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>579</v>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>71</v>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr">
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>55</v>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E709" t="n">
+      <c r="E733" t="n">
         <v>82.3</v>
       </c>
-      <c r="F709" t="inlineStr">
+      <c r="F733" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G709" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H709" t="inlineStr">
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -29330,7 +30290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -29857,175 +30817,200 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>88.51000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>81.3</v>
       </c>
       <c r="D21" t="n">
-        <v>88.86</v>
+        <v>85.38</v>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>84.84999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="G21" t="n">
-        <v>90.3</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84.47</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>81.5</v>
+        <v>83</v>
       </c>
       <c r="D22" t="n">
-        <v>84.98</v>
+        <v>88.86</v>
       </c>
       <c r="E22" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
-        <v>79.09999999999999</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>80.8</v>
+        <v>90.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="C23" t="n">
         <v>81.5</v>
       </c>
       <c r="D23" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="E23" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C24" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D24" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F24" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G24" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C25" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D25" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F25" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C26" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D26" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G26" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C27" t="n">
+        <v>82</v>
+      </c>
+      <c r="D27" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E27" t="n">
+        <v>68</v>
+      </c>
+      <c r="F27" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B28" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>85.34</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E28" t="n">
         <v>55</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -30040,7 +31025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -30536,171 +31521,190 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>23 August 2026</t>
+          <t>22 September 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>432035</v>
+        <v>378870</v>
       </c>
       <c r="C26" t="n">
-        <v>2847</v>
+        <v>2649</v>
       </c>
       <c r="D26" t="n">
-        <v>118099</v>
+        <v>104899</v>
       </c>
       <c r="E26" t="n">
-        <v>607</v>
+        <v>577</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 August 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>397374</v>
+        <v>432035</v>
       </c>
       <c r="C27" t="n">
-        <v>2775</v>
+        <v>2847</v>
       </c>
       <c r="D27" t="n">
-        <v>110421</v>
+        <v>118099</v>
       </c>
       <c r="E27" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>415586</v>
+        <v>397374</v>
       </c>
       <c r="C28" t="n">
-        <v>2788</v>
+        <v>2775</v>
       </c>
       <c r="D28" t="n">
-        <v>108294</v>
+        <v>110421</v>
       </c>
       <c r="E28" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="C29" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="D29" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="E29" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C30" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D30" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E30" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C31" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D31" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E31" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C32" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D32" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E32" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C33" t="n">
         <v>2778</v>
       </c>
       <c r="D33" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E33" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D34" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E34" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B35" t="n">
         <v>389862</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C35" t="n">
         <v>2676</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D35" t="n">
         <v>110408</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E35" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2746.92</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>396269.25</v>
+        <v>396881.62</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2746.75</v>
+        <v>2746.31</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396306.25</v>
+        <v>396840.85</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5493.67</v>
+        <v>5493.31</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>792575.5</v>
+        <v>793722.46</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>603.42</v>
+        <v>602.08</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>114515.58</v>
+        <v>113955</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>607.67</v>
+        <v>606.54</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90100.75</v>
+        <v>89824.23</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1211.08</v>
+        <v>1208.62</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204616.33</v>
+        <v>203779.23</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.64</v>
+        <v>92.59</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.66</v>
+        <v>88.05</v>
       </c>
     </row>
     <row r="16">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.34</v>
+        <v>82.64</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.09999999999999</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.84</v>
+        <v>95.01000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.8</v>
+        <v>80.86</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.09</v>
+        <v>81.23</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.31999999999999</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>85.06999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.6</v>
+        <v>61.55</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.34</v>
+        <v>87.38</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H733"/>
+  <dimension ref="A1:H757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23562,35 +23562,35 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>5528</v>
+        <v>96.7</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>5,528</t>
+          <t>96.70%</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -23602,35 +23602,35 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>792412</v>
+        <v>91.88</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>7,92,412</t>
+          <t>91.88%</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -23642,35 +23642,35 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>395038</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>3,95,038</t>
+          <t>85.71%</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -23682,35 +23682,35 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>2753</v>
+        <v>86</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>86.00%</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -23722,35 +23722,35 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>397374</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>3,97,374</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -23762,35 +23762,35 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>2775</v>
+        <v>40</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>2,775</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -23802,35 +23802,35 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>1183</v>
+        <v>87.84</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>1,183</t>
+          <t>87.84%</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -23842,35 +23842,35 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>199997</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>1,99,997</t>
+          <t>82.60%</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -23882,35 +23882,35 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>89576</v>
+        <v>85.7</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>89,576</t>
+          <t>85.70%</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -23922,35 +23922,35 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>596</v>
+        <v>71</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>71.00%</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -23962,35 +23962,35 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>110421</v>
+        <v>81.38</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>1,10,421</t>
+          <t>81.38%</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -24002,35 +24002,35 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>587</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>80.60%</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -24052,25 +24052,25 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>80.90000000000001</v>
+        <v>5528</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>80.90%</t>
+          <t>5,528</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -24092,25 +24092,25 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>72.42</v>
+        <v>792412</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>72.42%</t>
+          <t>7,92,412</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -24132,25 +24132,25 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>63.55</v>
+        <v>395038</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>63.55%</t>
+          <t>3,95,038</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -24172,25 +24172,25 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>80</v>
+        <v>2753</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
@@ -24212,25 +24212,25 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>82.5</v>
+        <v>397374</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>82.50%</t>
+          <t>3,97,374</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -24252,25 +24252,25 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>43.8</v>
+        <v>2775</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>43.80%</t>
+          <t>2,775</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -24292,25 +24292,25 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>84.47</v>
+        <v>1183</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>84.47%</t>
+          <t>1,183</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -24332,25 +24332,25 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>81.5</v>
+        <v>199997</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>1,99,997</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -24372,25 +24372,25 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>84.98</v>
+        <v>89576</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>84.98%</t>
+          <t>89,576</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -24412,25 +24412,25 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>65</v>
+        <v>596</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>65.00%</t>
+          <t>596</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
@@ -24452,25 +24452,25 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>79.09999999999999</v>
+        <v>110421</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>79.10%</t>
+          <t>1,10,421</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
@@ -24492,25 +24492,25 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>80.8</v>
+        <v>587</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>80.80%</t>
+          <t>587</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -24522,35 +24522,35 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>5576</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>80.90%</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -24562,35 +24562,35 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>833982</v>
+        <v>72.42</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>72.42%</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -24602,35 +24602,35 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>418396</v>
+        <v>63.55</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>63.55%</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -24642,35 +24642,35 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>2788</v>
+        <v>80</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -24682,35 +24682,35 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>415586</v>
+        <v>82.5</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>82.50%</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -24722,35 +24722,35 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2788</v>
+        <v>43.8</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>43.80%</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -24762,35 +24762,35 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>1141</v>
+        <v>84.47</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>84.47%</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
@@ -24802,35 +24802,35 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>190423</v>
+        <v>81.5</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -24842,35 +24842,35 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>82129</v>
+        <v>84.98</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>84.98%</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -24882,35 +24882,35 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>572</v>
+        <v>65</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>65.00%</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -24922,35 +24922,35 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>108294</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>79.10%</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -24962,35 +24962,35 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>569</v>
+        <v>80.8</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>80.80%</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -25002,35 +25002,35 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>90.31999999999999</v>
+        <v>5489</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -25042,35 +25042,35 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>93.51000000000001</v>
+        <v>807486</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>8,07,486</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
@@ -25082,35 +25082,35 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>74.27</v>
+        <v>403256</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>4,03,256</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -25122,35 +25122,35 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>84</v>
+        <v>2741</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>2,741</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
@@ -25162,35 +25162,35 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>92.09999999999999</v>
+        <v>404230</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,04,230</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
@@ -25202,35 +25202,35 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>30.8</v>
+        <v>2748</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>2,748</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -25242,35 +25242,35 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>88.58</v>
+        <v>1179</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>1,179</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -25282,35 +25282,35 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>81.5</v>
+        <v>193734</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>1,93,734</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H609" t="inlineStr">
@@ -25322,35 +25322,35 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>87.28</v>
+        <v>86506</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>86,506</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -25362,35 +25362,35 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>75</v>
+        <v>593</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -25402,35 +25402,35 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>84.11</v>
+        <v>107228</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>1,07,228</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -25442,35 +25442,35 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>82.7</v>
+        <v>586</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>586</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -25482,12 +25482,12 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -25501,11 +25501,11 @@
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5685</v>
+        <v>5576</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -25522,12 +25522,12 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -25541,11 +25541,11 @@
         </is>
       </c>
       <c r="E615" t="n">
-        <v>838364</v>
+        <v>833982</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -25562,12 +25562,12 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -25581,11 +25581,11 @@
         </is>
       </c>
       <c r="E616" t="n">
-        <v>414824</v>
+        <v>418396</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -25602,12 +25602,12 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -25621,11 +25621,11 @@
         </is>
       </c>
       <c r="E617" t="n">
-        <v>2833</v>
+        <v>2788</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -25642,12 +25642,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -25661,11 +25661,11 @@
         </is>
       </c>
       <c r="E618" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -25682,12 +25682,12 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -25701,11 +25701,11 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -25722,12 +25722,12 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -25741,11 +25741,11 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1218</v>
+        <v>1141</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -25762,12 +25762,12 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -25781,11 +25781,11 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>213243</v>
+        <v>190423</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -25802,12 +25802,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -25821,11 +25821,11 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>91058</v>
+        <v>82129</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -25842,12 +25842,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -25861,11 +25861,11 @@
         </is>
       </c>
       <c r="E623" t="n">
-        <v>611</v>
+        <v>572</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -25882,12 +25882,12 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -25901,11 +25901,11 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -25922,12 +25922,12 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -25941,11 +25941,11 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -25962,12 +25962,12 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -25981,11 +25981,11 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>89.66</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -26002,12 +26002,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -26021,11 +26021,11 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>92.28</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -26042,12 +26042,12 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -26061,11 +26061,11 @@
         </is>
       </c>
       <c r="E628" t="n">
-        <v>77.13</v>
+        <v>74.27</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -26082,12 +26082,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -26101,11 +26101,11 @@
         </is>
       </c>
       <c r="E629" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -26122,12 +26122,12 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -26141,11 +26141,11 @@
         </is>
       </c>
       <c r="E630" t="n">
-        <v>94.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -26162,12 +26162,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -26181,11 +26181,11 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>41.2</v>
+        <v>30.8</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -26202,12 +26202,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -26221,11 +26221,11 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -26242,12 +26242,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -26261,11 +26261,11 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -26282,12 +26282,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -26301,11 +26301,11 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -26322,12 +26322,12 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -26341,11 +26341,11 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -26362,12 +26362,12 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -26381,11 +26381,11 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -26402,12 +26402,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -26421,11 +26421,11 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -26442,35 +26442,35 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -26482,35 +26482,35 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -26522,35 +26522,35 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -26562,35 +26562,35 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -26602,35 +26602,35 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -26642,35 +26642,35 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -26682,35 +26682,35 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -26722,35 +26722,35 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -26762,35 +26762,35 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -26802,35 +26802,35 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -26842,35 +26842,35 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -26882,35 +26882,35 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -26922,35 +26922,35 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -26962,35 +26962,35 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -27002,35 +27002,35 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -27042,35 +27042,35 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -27082,35 +27082,35 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -27122,35 +27122,35 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -27162,35 +27162,35 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -27202,35 +27202,35 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -27242,35 +27242,35 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -27282,35 +27282,35 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -27322,35 +27322,35 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -27362,35 +27362,35 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -27402,35 +27402,35 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -27442,35 +27442,35 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -27482,35 +27482,35 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -27522,35 +27522,35 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -27562,35 +27562,35 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -27602,35 +27602,35 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -27642,35 +27642,35 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -27682,35 +27682,35 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -27722,35 +27722,35 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -27762,35 +27762,35 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -27802,35 +27802,35 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -27842,35 +27842,35 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -27882,12 +27882,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -27901,11 +27901,11 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -27922,12 +27922,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -27941,11 +27941,11 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -27962,12 +27962,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -27981,11 +27981,11 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -28002,12 +28002,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28021,11 +28021,11 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -28042,12 +28042,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28061,11 +28061,11 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -28082,12 +28082,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28101,11 +28101,11 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -28122,12 +28122,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28141,11 +28141,11 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -28162,12 +28162,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28181,11 +28181,11 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -28202,12 +28202,12 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -28221,11 +28221,11 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -28242,12 +28242,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -28261,11 +28261,11 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -28282,12 +28282,12 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -28301,11 +28301,11 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -28322,12 +28322,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -28341,11 +28341,11 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -28362,12 +28362,12 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -28381,11 +28381,11 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -28402,12 +28402,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -28421,11 +28421,11 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -28442,12 +28442,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -28461,11 +28461,11 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -28482,12 +28482,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -28501,11 +28501,11 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -28522,12 +28522,12 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -28541,11 +28541,11 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -28562,12 +28562,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -28581,11 +28581,11 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -28602,12 +28602,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -28621,11 +28621,11 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -28642,12 +28642,12 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -28661,11 +28661,11 @@
         </is>
       </c>
       <c r="E693" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -28682,12 +28682,12 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -28701,11 +28701,11 @@
         </is>
       </c>
       <c r="E694" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -28722,12 +28722,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -28741,11 +28741,11 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -28762,12 +28762,12 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -28781,11 +28781,11 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -28802,12 +28802,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -28821,11 +28821,11 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -28842,35 +28842,35 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -28882,35 +28882,35 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -28922,35 +28922,35 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -28962,35 +28962,35 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -29002,35 +29002,35 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -29042,35 +29042,35 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -29082,35 +29082,35 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -29122,35 +29122,35 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -29162,35 +29162,35 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -29202,35 +29202,35 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -29242,35 +29242,35 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -29282,35 +29282,35 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -29322,12 +29322,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -29341,11 +29341,11 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -29362,12 +29362,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -29381,11 +29381,11 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -29402,12 +29402,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -29421,11 +29421,11 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -29442,12 +29442,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -29461,11 +29461,11 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -29482,12 +29482,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -29501,11 +29501,11 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -29522,12 +29522,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -29541,11 +29541,11 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -29562,12 +29562,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -29581,11 +29581,11 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -29602,12 +29602,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -29621,11 +29621,11 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -29642,12 +29642,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -29661,11 +29661,11 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -29682,12 +29682,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -29701,11 +29701,11 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -29722,12 +29722,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -29741,11 +29741,11 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -29762,12 +29762,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -29781,11 +29781,11 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -29802,12 +29802,12 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -29821,11 +29821,11 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -29842,12 +29842,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -29861,11 +29861,11 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -29882,12 +29882,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -29901,11 +29901,11 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -29922,12 +29922,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -29941,11 +29941,11 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -29962,12 +29962,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -29981,11 +29981,11 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -30002,12 +30002,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30021,11 +30021,11 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -30042,12 +30042,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30061,11 +30061,11 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -30082,12 +30082,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30101,11 +30101,11 @@
         </is>
       </c>
       <c r="E729" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -30122,12 +30122,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -30141,11 +30141,11 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -30162,12 +30162,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -30181,11 +30181,11 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -30202,12 +30202,12 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -30221,11 +30221,11 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -30242,38 +30242,998 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B733" t="inlineStr">
+      <c r="B734" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr">
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>576</v>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>579</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>71</v>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr">
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>55</v>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E733" t="n">
+      <c r="E757" t="n">
         <v>82.3</v>
       </c>
-      <c r="F733" t="inlineStr">
+      <c r="F757" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G733" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H733" t="inlineStr">
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -30290,7 +31250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -30867,150 +31827,175 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>24 August 2026</t>
+          <t>23 September 2026</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.47</v>
+        <v>87.84</v>
       </c>
       <c r="C23" t="n">
-        <v>81.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>84.98</v>
+        <v>85.7</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
-        <v>79.09999999999999</v>
+        <v>81.38</v>
       </c>
       <c r="G23" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 August 2026</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88.58</v>
+        <v>84.47</v>
       </c>
       <c r="C24" t="n">
         <v>81.5</v>
       </c>
       <c r="D24" t="n">
-        <v>87.28</v>
+        <v>84.98</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>84.11</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>82.7</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C25" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D25" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E25" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G25" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C26" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D26" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F26" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C27" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D27" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G27" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C28" t="n">
+        <v>82</v>
+      </c>
+      <c r="D28" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>68</v>
+      </c>
+      <c r="F28" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G28" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B29" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C29" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D29" t="n">
         <v>85.34</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>55</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F29" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G29" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -31025,7 +32010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -31578,133 +32563,152 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>415586</v>
+        <v>404230</v>
       </c>
       <c r="C29" t="n">
-        <v>2788</v>
+        <v>2748</v>
       </c>
       <c r="D29" t="n">
-        <v>108294</v>
+        <v>107228</v>
       </c>
       <c r="E29" t="n">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>423540</v>
+        <v>415586</v>
       </c>
       <c r="C30" t="n">
-        <v>2852</v>
+        <v>2788</v>
       </c>
       <c r="D30" t="n">
-        <v>122185</v>
+        <v>108294</v>
       </c>
       <c r="E30" t="n">
-        <v>607</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C31" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D31" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E31" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C32" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D32" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E32" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C33" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D33" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E33" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C34" t="n">
         <v>2778</v>
       </c>
       <c r="D34" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E34" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D35" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E35" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B36" t="n">
         <v>389862</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>2676</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D36" t="n">
         <v>110408</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E36" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.59</v>
+        <v>92.45999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.05</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.98</v>
+        <v>39.43</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.64</v>
+        <v>82.45999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76.09</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>95.01000000000001</v>
+        <v>94.75</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80.86</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.23</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.16</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85.06999999999999</v>
+        <v>85.20999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.55</v>
+        <v>60.42</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.38</v>
+        <v>87.42</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H757"/>
+  <dimension ref="A1:H769"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -25482,35 +25482,35 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>5576</v>
+        <v>91.94</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>5,576</t>
+          <t>91.94%</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
@@ -25522,35 +25522,35 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>833982</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>8,33,982</t>
+          <t>84.43%</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -25562,35 +25562,35 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>418396</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>4,18,396</t>
+          <t>80.49%</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -25602,35 +25602,35 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>2788</v>
+        <v>74</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>74.00%</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -25642,35 +25642,35 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>415586</v>
+        <v>91</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>4,15,586</t>
+          <t>91.00%</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -25682,35 +25682,35 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>2788</v>
+        <v>33.3</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>2,788</t>
+          <t>33.30%</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -25722,35 +25722,35 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1141</v>
+        <v>87.8</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>1,141</t>
+          <t>87.80%</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -25762,35 +25762,35 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>190423</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>1,90,423</t>
+          <t>84.60%</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -25802,35 +25802,35 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>82129</v>
+        <v>86.73</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>82,129</t>
+          <t>86.73%</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -25842,35 +25842,35 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>572</v>
+        <v>48</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>48.00%</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -25882,35 +25882,35 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>108294</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>1,08,294</t>
+          <t>82.68%</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -25922,35 +25922,35 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>569</v>
+        <v>81.2</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>81.20%</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -25972,25 +25972,25 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>90.31999999999999</v>
+        <v>5576</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>90.32%</t>
+          <t>5,576</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -26012,25 +26012,25 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>93.51000000000001</v>
+        <v>833982</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>93.51%</t>
+          <t>8,33,982</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -26052,25 +26052,25 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>74.27</v>
+        <v>418396</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>74.27%</t>
+          <t>4,18,396</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -26092,25 +26092,25 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>84</v>
+        <v>2788</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>84.00%</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -26132,25 +26132,25 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>92.09999999999999</v>
+        <v>415586</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,15,586</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -26172,25 +26172,25 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>30.8</v>
+        <v>2788</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>30.80%</t>
+          <t>2,788</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -26212,25 +26212,25 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>88.58</v>
+        <v>1141</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>88.58%</t>
+          <t>1,141</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -26252,25 +26252,25 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>81.5</v>
+        <v>190423</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>81.50%</t>
+          <t>1,90,423</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -26292,25 +26292,25 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>87.28</v>
+        <v>82129</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>87.28%</t>
+          <t>82,129</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -26332,25 +26332,25 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>75</v>
+        <v>572</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>75.00%</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -26372,25 +26372,25 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>84.11</v>
+        <v>108294</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>84.11%</t>
+          <t>1,08,294</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -26412,25 +26412,25 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>82.7</v>
+        <v>569</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>82.70%</t>
+          <t>569</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -26442,35 +26442,35 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>5685</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -26482,35 +26482,35 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>838364</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>93.51%</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -26522,35 +26522,35 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>414824</v>
+        <v>74.27</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>74.27%</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -26562,35 +26562,35 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>2833</v>
+        <v>84</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>84.00%</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
@@ -26602,35 +26602,35 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>423540</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -26642,35 +26642,35 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>2852</v>
+        <v>30.8</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>30.80%</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -26682,35 +26682,35 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1218</v>
+        <v>88.58</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>88.58%</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -26722,35 +26722,35 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>213243</v>
+        <v>81.5</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>81.50%</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -26762,35 +26762,35 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>91058</v>
+        <v>87.28</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>87.28%</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -26802,35 +26802,35 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>611</v>
+        <v>75</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>75.00%</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -26842,35 +26842,35 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>122185</v>
+        <v>84.11</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>84.11%</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -26882,35 +26882,35 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>607</v>
+        <v>82.7</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>82.70%</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
@@ -26932,25 +26932,25 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>89.66</v>
+        <v>5685</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
@@ -26972,25 +26972,25 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>92.28</v>
+        <v>838364</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
@@ -27012,25 +27012,25 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>77.13</v>
+        <v>414824</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
@@ -27052,25 +27052,25 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>72</v>
+        <v>2833</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
@@ -27092,25 +27092,25 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>94.3</v>
+        <v>423540</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -27132,25 +27132,25 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>41.2</v>
+        <v>2852</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H655" t="inlineStr">
@@ -27172,25 +27172,25 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>91.44</v>
+        <v>1218</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -27212,25 +27212,25 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>83.3</v>
+        <v>213243</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -27252,25 +27252,25 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>87.06999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -27292,25 +27292,25 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>72</v>
+        <v>611</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -27332,25 +27332,25 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>84.88</v>
+        <v>122185</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -27372,25 +27372,25 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>92.2</v>
+        <v>607</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -27402,12 +27402,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -27421,11 +27421,11 @@
         </is>
       </c>
       <c r="E662" t="n">
-        <v>97.44</v>
+        <v>89.66</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -27442,12 +27442,12 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -27461,11 +27461,11 @@
         </is>
       </c>
       <c r="E663" t="n">
-        <v>95.38</v>
+        <v>92.28</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -27482,12 +27482,12 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -27501,11 +27501,11 @@
         </is>
       </c>
       <c r="E664" t="n">
-        <v>95.59999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -27522,12 +27522,12 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -27541,11 +27541,11 @@
         </is>
       </c>
       <c r="E665" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -27562,12 +27562,12 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -27581,11 +27581,11 @@
         </is>
       </c>
       <c r="E666" t="n">
-        <v>92.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -27602,12 +27602,12 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -27621,11 +27621,11 @@
         </is>
       </c>
       <c r="E667" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -27642,12 +27642,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -27661,11 +27661,11 @@
         </is>
       </c>
       <c r="E668" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -27682,12 +27682,12 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -27701,11 +27701,11 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -27722,12 +27722,12 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -27741,11 +27741,11 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -27762,12 +27762,12 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -27781,11 +27781,11 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -27802,12 +27802,12 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -27821,11 +27821,11 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -27842,12 +27842,12 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -27861,11 +27861,11 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -27887,30 +27887,30 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -27927,30 +27927,30 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -27967,30 +27967,30 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -28007,30 +28007,30 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -28047,30 +28047,30 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -28087,30 +28087,30 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -28127,30 +28127,30 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -28167,30 +28167,30 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -28207,30 +28207,30 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -28247,30 +28247,30 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -28287,30 +28287,30 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -28327,30 +28327,30 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -28362,12 +28362,12 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -28381,11 +28381,11 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5532</v>
+        <v>5393</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -28402,12 +28402,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -28421,11 +28421,11 @@
         </is>
       </c>
       <c r="E687" t="n">
-        <v>781659</v>
+        <v>766540</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -28442,12 +28442,12 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -28461,11 +28461,11 @@
         </is>
       </c>
       <c r="E688" t="n">
-        <v>389707</v>
+        <v>382785</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -28482,12 +28482,12 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -28501,11 +28501,11 @@
         </is>
       </c>
       <c r="E689" t="n">
-        <v>2753</v>
+        <v>2695</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -28522,12 +28522,12 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -28541,11 +28541,11 @@
         </is>
       </c>
       <c r="E690" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -28562,12 +28562,12 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -28581,11 +28581,11 @@
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -28602,12 +28602,12 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -28621,11 +28621,11 @@
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1234</v>
+        <v>1175</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -28642,12 +28642,12 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -28661,11 +28661,11 @@
         </is>
       </c>
       <c r="E693" t="n">
-        <v>211783</v>
+        <v>213994</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -28682,12 +28682,12 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -28701,11 +28701,11 @@
         </is>
       </c>
       <c r="E694" t="n">
-        <v>90299</v>
+        <v>105543</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -28722,12 +28722,12 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -28741,11 +28741,11 @@
         </is>
       </c>
       <c r="E695" t="n">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -28762,12 +28762,12 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -28781,11 +28781,11 @@
         </is>
       </c>
       <c r="E696" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -28802,12 +28802,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -28821,11 +28821,11 @@
         </is>
       </c>
       <c r="E697" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -28842,12 +28842,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -28861,11 +28861,11 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>5568</v>
+        <v>5532</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -28882,12 +28882,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -28901,11 +28901,11 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>783117</v>
+        <v>781659</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -28922,12 +28922,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -28941,11 +28941,11 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>392017</v>
+        <v>389707</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -28962,12 +28962,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -28981,11 +28981,11 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2790</v>
+        <v>2753</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29021,11 +29021,11 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -29042,12 +29042,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29061,11 +29061,11 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -29082,12 +29082,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29101,11 +29101,11 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1243</v>
+        <v>1234</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -29122,12 +29122,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29141,11 +29141,11 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>217252</v>
+        <v>211783</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -29162,12 +29162,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -29181,11 +29181,11 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>97836</v>
+        <v>90299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -29202,12 +29202,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -29221,11 +29221,11 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -29242,12 +29242,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -29261,11 +29261,11 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -29282,12 +29282,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -29301,11 +29301,11 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -29322,12 +29322,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -29341,11 +29341,11 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>5552</v>
+        <v>5568</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -29362,12 +29362,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -29381,11 +29381,11 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>824283</v>
+        <v>783117</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -29402,12 +29402,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -29421,11 +29421,11 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>410895</v>
+        <v>392017</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -29442,12 +29442,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -29461,11 +29461,11 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>2774</v>
+        <v>2790</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -29482,12 +29482,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -29501,11 +29501,11 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -29522,12 +29522,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -29562,12 +29562,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -29581,11 +29581,11 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1223</v>
+        <v>1243</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -29602,12 +29602,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -29621,11 +29621,11 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>206128</v>
+        <v>217252</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -29642,12 +29642,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -29661,11 +29661,11 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>89897</v>
+        <v>97836</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -29682,12 +29682,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -29701,11 +29701,11 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -29722,12 +29722,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -29741,11 +29741,11 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -29762,12 +29762,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -29781,11 +29781,11 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -29812,25 +29812,25 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>86.67</v>
+        <v>5552</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -29852,25 +29852,25 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>83.43000000000001</v>
+        <v>824283</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -29892,25 +29892,25 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>85.90000000000001</v>
+        <v>410895</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -29932,25 +29932,25 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>85</v>
+        <v>2774</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -29972,25 +29972,25 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>90.09999999999999</v>
+        <v>413388</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -30012,25 +30012,25 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -30052,25 +30052,25 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>87.38</v>
+        <v>1223</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -30092,25 +30092,25 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>82</v>
+        <v>206128</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -30132,25 +30132,25 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>85.56999999999999</v>
+        <v>89897</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -30172,25 +30172,25 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>68</v>
+        <v>620</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -30212,25 +30212,25 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>83.55</v>
+        <v>116231</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -30252,25 +30252,25 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>83.09999999999999</v>
+        <v>603</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -30282,35 +30282,35 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>5347</v>
+        <v>86.67</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -30322,35 +30322,35 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>776545</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -30362,35 +30362,35 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>386683</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -30402,35 +30402,35 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E737" t="n">
-        <v>2671</v>
+        <v>85</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -30442,35 +30442,35 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>389862</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -30482,35 +30482,35 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E739" t="n">
-        <v>2676</v>
+        <v>40</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -30522,35 +30522,35 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>1155</v>
+        <v>87.38</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -30562,35 +30562,35 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>191354</v>
+        <v>82</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -30602,35 +30602,35 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>80946</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -30642,35 +30642,35 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>576</v>
+        <v>68</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -30682,35 +30682,35 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>110408</v>
+        <v>83.55</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -30722,35 +30722,35 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>579</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>83.10%</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -30772,25 +30772,25 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>97.75</v>
+        <v>5347</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>5,347</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -30812,25 +30812,25 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>89.15000000000001</v>
+        <v>776545</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>7,76,545</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -30852,25 +30852,25 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>77.83</v>
+        <v>386683</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>3,86,683</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -30892,25 +30892,25 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>71</v>
+        <v>2671</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>2,671</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -30932,25 +30932,25 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>94.3</v>
+        <v>389862</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>3,89,862</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -30972,25 +30972,25 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>42.9</v>
+        <v>2676</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>2,676</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -31012,25 +31012,25 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>86.84999999999999</v>
+        <v>1155</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>1,155</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -31052,25 +31052,25 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>81.40000000000001</v>
+        <v>191354</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>1,91,354</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -31092,25 +31092,25 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>85.34</v>
+        <v>80946</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>80,946</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -31132,25 +31132,25 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E755" t="n">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>576</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -31172,25 +31172,25 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>81.51000000000001</v>
+        <v>110408</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>1,10,408</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -31212,28 +31212,508 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>579</v>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>71</v>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D757" t="inlineStr">
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>55</v>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E757" t="n">
+      <c r="E769" t="n">
         <v>82.3</v>
       </c>
-      <c r="F757" t="inlineStr">
+      <c r="F769" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G757" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H757" t="inlineStr">
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -31250,7 +31730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -31877,125 +32357,150 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26 August 2026</t>
+          <t>24 September 2026</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>88.58</v>
+        <v>87.8</v>
       </c>
       <c r="C25" t="n">
-        <v>81.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>87.28</v>
+        <v>86.73</v>
       </c>
       <c r="E25" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>84.11</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>82.7</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 August 2026</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>91.44</v>
+        <v>88.58</v>
       </c>
       <c r="C26" t="n">
-        <v>83.3</v>
+        <v>81.5</v>
       </c>
       <c r="D26" t="n">
-        <v>87.06999999999999</v>
+        <v>87.28</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F26" t="n">
-        <v>84.88</v>
+        <v>84.11</v>
       </c>
       <c r="G26" t="n">
-        <v>92.2</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C27" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D27" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F27" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C28" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D28" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G28" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C29" t="n">
+        <v>82</v>
+      </c>
+      <c r="D29" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>68</v>
+      </c>
+      <c r="F29" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G29" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C30" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>85.34</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E30" t="n">
         <v>55</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G30" t="n">
         <v>82.3</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2747</v>
+        <v>2745.86</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>396881.62</v>
+        <v>397446.64</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2746.31</v>
+        <v>2744.71</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>396840.85</v>
+        <v>397009.43</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5493.31</v>
+        <v>5490.57</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>793722.46</v>
+        <v>794456.0699999999</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>602.08</v>
+        <v>602.79</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>113955</v>
+        <v>114182.07</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>606.54</v>
+        <v>607.0700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>89824.23</v>
+        <v>90362.21000000001</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1208.62</v>
+        <v>1209.86</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>203779.23</v>
+        <v>204544.29</v>
       </c>
     </row>
     <row r="14">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H769"/>
+  <dimension ref="A1:H781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -26922,12 +26922,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -26941,11 +26941,11 @@
         </is>
       </c>
       <c r="E650" t="n">
-        <v>5685</v>
+        <v>5455</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,455</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -26962,12 +26962,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -26981,11 +26981,11 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>838364</v>
+        <v>803993</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>8,03,993</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -27002,12 +27002,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -27021,11 +27021,11 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>414824</v>
+        <v>399201</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>3,99,201</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -27042,12 +27042,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -27061,11 +27061,11 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>2833</v>
+        <v>2724</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,724</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -27082,12 +27082,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -27101,11 +27101,11 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>423540</v>
+        <v>404792</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>4,04,792</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -27122,12 +27122,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -27141,11 +27141,11 @@
         </is>
       </c>
       <c r="E655" t="n">
-        <v>2852</v>
+        <v>2731</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,731</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -27162,12 +27162,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -27181,11 +27181,11 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,226</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -27202,12 +27202,12 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -27221,11 +27221,11 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>213243</v>
+        <v>214490</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>2,14,490</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -27242,12 +27242,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -27261,11 +27261,11 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>91058</v>
+        <v>97356</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>97,356</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -27282,12 +27282,12 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -27301,11 +27301,11 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -27322,12 +27322,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -27341,11 +27341,11 @@
         </is>
       </c>
       <c r="E660" t="n">
-        <v>122185</v>
+        <v>117134</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,17,134</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -27362,12 +27362,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -27381,11 +27381,11 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -27412,25 +27412,25 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>89.66</v>
+        <v>5685</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -27452,25 +27452,25 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>92.28</v>
+        <v>838364</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -27492,25 +27492,25 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>77.13</v>
+        <v>414824</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -27532,25 +27532,25 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>72</v>
+        <v>2833</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -27572,25 +27572,25 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>94.3</v>
+        <v>423540</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -27612,25 +27612,25 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>41.2</v>
+        <v>2852</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -27652,25 +27652,25 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>91.44</v>
+        <v>1218</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -27692,25 +27692,25 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>83.3</v>
+        <v>213243</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -27732,25 +27732,25 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>87.06999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -27772,25 +27772,25 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>72</v>
+        <v>611</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -27812,25 +27812,25 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>84.88</v>
+        <v>122185</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -27852,25 +27852,25 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>92.2</v>
+        <v>607</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -27882,12 +27882,12 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -27901,11 +27901,11 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>97.44</v>
+        <v>89.66</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -27922,12 +27922,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -27941,11 +27941,11 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>95.38</v>
+        <v>92.28</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -27962,12 +27962,12 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -27981,11 +27981,11 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>95.59999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -28002,12 +28002,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -28021,11 +28021,11 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -28042,12 +28042,12 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -28061,11 +28061,11 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>92.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -28082,12 +28082,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -28101,11 +28101,11 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -28122,12 +28122,12 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -28141,11 +28141,11 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -28162,12 +28162,12 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -28181,11 +28181,11 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -28202,12 +28202,12 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -28221,11 +28221,11 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -28242,12 +28242,12 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -28261,11 +28261,11 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -28282,12 +28282,12 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -28301,11 +28301,11 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -28322,12 +28322,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -28341,11 +28341,11 @@
         </is>
       </c>
       <c r="E685" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -28367,30 +28367,30 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -28407,30 +28407,30 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -28447,30 +28447,30 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -28487,30 +28487,30 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -28527,30 +28527,30 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -28567,30 +28567,30 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -28607,30 +28607,30 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -28647,30 +28647,30 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -28687,30 +28687,30 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -28727,30 +28727,30 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -28767,30 +28767,30 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -28807,30 +28807,30 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -28842,12 +28842,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -28861,11 +28861,11 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>5532</v>
+        <v>5393</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -28882,12 +28882,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -28901,11 +28901,11 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>781659</v>
+        <v>766540</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -28922,12 +28922,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -28941,11 +28941,11 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>389707</v>
+        <v>382785</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -28962,12 +28962,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -28981,11 +28981,11 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2753</v>
+        <v>2695</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29021,11 +29021,11 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -29042,12 +29042,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29061,11 +29061,11 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -29082,12 +29082,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29101,11 +29101,11 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1234</v>
+        <v>1175</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -29122,12 +29122,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29141,11 +29141,11 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>211783</v>
+        <v>213994</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -29162,12 +29162,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -29181,11 +29181,11 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>90299</v>
+        <v>105543</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -29202,12 +29202,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -29221,11 +29221,11 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -29242,12 +29242,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -29261,11 +29261,11 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -29282,12 +29282,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -29301,11 +29301,11 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -29322,12 +29322,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -29341,11 +29341,11 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>5568</v>
+        <v>5532</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -29362,12 +29362,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -29381,11 +29381,11 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>783117</v>
+        <v>781659</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -29402,12 +29402,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -29421,11 +29421,11 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>392017</v>
+        <v>389707</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -29442,12 +29442,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -29461,11 +29461,11 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>2790</v>
+        <v>2753</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -29482,12 +29482,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -29501,11 +29501,11 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -29522,12 +29522,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -29541,11 +29541,11 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -29562,12 +29562,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -29581,11 +29581,11 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1243</v>
+        <v>1234</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -29602,12 +29602,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -29621,11 +29621,11 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>217252</v>
+        <v>211783</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -29642,12 +29642,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -29661,11 +29661,11 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>97836</v>
+        <v>90299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -29682,12 +29682,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -29701,11 +29701,11 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -29722,12 +29722,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -29741,11 +29741,11 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -29762,12 +29762,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -29781,11 +29781,11 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -29802,12 +29802,12 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -29821,11 +29821,11 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>5552</v>
+        <v>5568</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -29842,12 +29842,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -29861,11 +29861,11 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>824283</v>
+        <v>783117</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -29882,12 +29882,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -29901,11 +29901,11 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>410895</v>
+        <v>392017</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -29922,12 +29922,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -29941,11 +29941,11 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2774</v>
+        <v>2790</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -29962,12 +29962,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -29981,11 +29981,11 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -30002,12 +30002,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30042,12 +30042,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30061,11 +30061,11 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1223</v>
+        <v>1243</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -30082,12 +30082,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30101,11 +30101,11 @@
         </is>
       </c>
       <c r="E729" t="n">
-        <v>206128</v>
+        <v>217252</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -30122,12 +30122,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -30141,11 +30141,11 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>89897</v>
+        <v>97836</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -30162,12 +30162,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -30181,11 +30181,11 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -30202,12 +30202,12 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -30221,11 +30221,11 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -30242,12 +30242,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -30261,11 +30261,11 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -30292,25 +30292,25 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>86.67</v>
+        <v>5552</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -30332,25 +30332,25 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>83.43000000000001</v>
+        <v>824283</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -30372,25 +30372,25 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>85.90000000000001</v>
+        <v>410895</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -30412,25 +30412,25 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E737" t="n">
-        <v>85</v>
+        <v>2774</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -30452,25 +30452,25 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>90.09999999999999</v>
+        <v>413388</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -30492,25 +30492,25 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E739" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -30532,25 +30532,25 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>87.38</v>
+        <v>1223</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -30572,25 +30572,25 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>82</v>
+        <v>206128</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -30612,25 +30612,25 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>85.56999999999999</v>
+        <v>89897</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -30652,25 +30652,25 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>68</v>
+        <v>620</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -30692,25 +30692,25 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>83.55</v>
+        <v>116231</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -30732,25 +30732,25 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>83.09999999999999</v>
+        <v>603</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -30762,35 +30762,35 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>5347</v>
+        <v>86.67</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -30802,35 +30802,35 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>776545</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -30842,35 +30842,35 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>386683</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -30882,35 +30882,35 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>2671</v>
+        <v>85</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -30922,35 +30922,35 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>389862</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -30962,35 +30962,35 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2676</v>
+        <v>40</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -31002,35 +31002,35 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>1155</v>
+        <v>87.38</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -31042,35 +31042,35 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>191354</v>
+        <v>82</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -31082,35 +31082,35 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>80946</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -31122,35 +31122,35 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E755" t="n">
-        <v>576</v>
+        <v>68</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -31162,35 +31162,35 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>110408</v>
+        <v>83.55</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -31202,35 +31202,35 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E757" t="n">
-        <v>579</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>83.10%</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -31252,25 +31252,25 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E758" t="n">
-        <v>97.75</v>
+        <v>5347</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>5,347</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
@@ -31292,25 +31292,25 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E759" t="n">
-        <v>89.15000000000001</v>
+        <v>776545</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>7,76,545</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -31332,25 +31332,25 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E760" t="n">
-        <v>77.83</v>
+        <v>386683</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>3,86,683</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -31372,25 +31372,25 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E761" t="n">
-        <v>71</v>
+        <v>2671</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>2,671</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
@@ -31412,25 +31412,25 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E762" t="n">
-        <v>94.3</v>
+        <v>389862</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>3,89,862</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -31452,25 +31452,25 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E763" t="n">
-        <v>42.9</v>
+        <v>2676</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>2,676</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -31492,25 +31492,25 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E764" t="n">
-        <v>86.84999999999999</v>
+        <v>1155</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>1,155</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -31532,25 +31532,25 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E765" t="n">
-        <v>81.40000000000001</v>
+        <v>191354</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>1,91,354</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
@@ -31572,25 +31572,25 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>85.34</v>
+        <v>80946</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>80,946</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -31612,25 +31612,25 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E767" t="n">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>576</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
@@ -31652,25 +31652,25 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D768" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E768" t="n">
-        <v>81.51000000000001</v>
+        <v>110408</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>1,10,408</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -31692,28 +31692,508 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>579</v>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>71</v>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr">
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>55</v>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E769" t="n">
+      <c r="E781" t="n">
         <v>82.3</v>
       </c>
-      <c r="F769" t="inlineStr">
+      <c r="F781" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G769" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H769" t="inlineStr">
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -32515,7 +32995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -33106,114 +33586,133 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>26 September 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>423540</v>
+        <v>404792</v>
       </c>
       <c r="C31" t="n">
-        <v>2852</v>
+        <v>2731</v>
       </c>
       <c r="D31" t="n">
-        <v>122185</v>
+        <v>117134</v>
       </c>
       <c r="E31" t="n">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C32" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D32" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E32" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C33" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D33" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E33" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C34" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D34" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E34" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C35" t="n">
         <v>2778</v>
       </c>
       <c r="D35" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E35" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D36" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E36" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B37" t="n">
         <v>389862</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>2676</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>110408</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2745.86</v>
+        <v>2747.2</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>397446.64</v>
+        <v>398077.33</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2744.71</v>
+        <v>2745.93</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>397009.43</v>
+        <v>397576.13</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5490.57</v>
+        <v>5493.13</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>794456.0699999999</v>
+        <v>795653.47</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>602.79</v>
+        <v>602.73</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>114182.07</v>
+        <v>113945.8</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>607.0700000000001</v>
+        <v>607.2</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90362.21000000001</v>
+        <v>90759</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1209.86</v>
+        <v>1209.93</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204544.29</v>
+        <v>204704.8</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.45999999999999</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>87.75</v>
+        <v>88.15000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.43</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="17">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75.92</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.75</v>
+        <v>94.45999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81.01000000000001</v>
+        <v>81.37</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.51000000000001</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.08</v>
+        <v>82.92</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85.20999999999999</v>
+        <v>85.64</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60.42</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.42</v>
+        <v>87.64</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H781"/>
+  <dimension ref="A1:H805"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27402,35 +27402,35 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>5685</v>
+        <v>90.91</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
@@ -27442,35 +27442,35 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E663" t="n">
-        <v>838364</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>92.99%</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
@@ -27482,35 +27482,35 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>414824</v>
+        <v>82.41</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>82.41%</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
@@ -27522,35 +27522,35 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2833</v>
+        <v>89</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>89.00%</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
@@ -27562,35 +27562,35 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>423540</v>
+        <v>94.8</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>94.80%</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -27602,35 +27602,35 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>2852</v>
+        <v>46.7</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>46.70%</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
@@ -27642,35 +27642,35 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E668" t="n">
-        <v>1218</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>90.32%</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -27682,35 +27682,35 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E669" t="n">
-        <v>213243</v>
+        <v>87.2</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>87.20%</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
@@ -27722,35 +27722,35 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E670" t="n">
-        <v>91058</v>
+        <v>90.86</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>90.86%</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -27762,35 +27762,35 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E671" t="n">
-        <v>611</v>
+        <v>71</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>71.00%</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -27802,35 +27802,35 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E672" t="n">
-        <v>122185</v>
+        <v>85.69</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>85.69%</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
@@ -27842,35 +27842,35 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E673" t="n">
-        <v>607</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>92.90%</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -27882,35 +27882,35 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E674" t="n">
-        <v>89.66</v>
+        <v>5529</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>5,529</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
@@ -27922,35 +27922,35 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E675" t="n">
-        <v>92.28</v>
+        <v>812417</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>8,12,417</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -27962,35 +27962,35 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E676" t="n">
-        <v>77.13</v>
+        <v>405510</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>4,05,510</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
@@ -28002,35 +28002,35 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E677" t="n">
-        <v>72</v>
+        <v>2763</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>2,763</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -28042,35 +28042,35 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E678" t="n">
-        <v>94.3</v>
+        <v>406907</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>4,06,907</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -28082,35 +28082,35 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E679" t="n">
-        <v>41.2</v>
+        <v>2766</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>2,766</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -28122,35 +28122,35 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E680" t="n">
-        <v>91.44</v>
+        <v>1211</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -28162,35 +28162,35 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E681" t="n">
-        <v>83.3</v>
+        <v>206952</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>2,06,952</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -28202,35 +28202,35 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E682" t="n">
-        <v>87.06999999999999</v>
+        <v>96314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>96,314</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
@@ -28242,35 +28242,35 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E683" t="n">
-        <v>72</v>
+        <v>609</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>609</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -28282,35 +28282,35 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E684" t="n">
-        <v>84.88</v>
+        <v>110638</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>1,10,638</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -28322,35 +28322,35 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E685" t="n">
-        <v>92.2</v>
+        <v>602</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>602</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
@@ -28362,35 +28362,35 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -28402,35 +28402,35 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -28442,35 +28442,35 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -28482,35 +28482,35 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -28522,35 +28522,35 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -28562,35 +28562,35 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -28602,35 +28602,35 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -28642,35 +28642,35 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -28682,35 +28682,35 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -28722,35 +28722,35 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -28762,35 +28762,35 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -28802,35 +28802,35 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -28842,35 +28842,35 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -28882,35 +28882,35 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -28922,35 +28922,35 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -28962,35 +28962,35 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -29002,35 +29002,35 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -29042,35 +29042,35 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -29082,35 +29082,35 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -29122,35 +29122,35 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -29162,35 +29162,35 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -29202,35 +29202,35 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -29242,35 +29242,35 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -29282,35 +29282,35 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -29322,35 +29322,35 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -29362,35 +29362,35 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -29402,35 +29402,35 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -29442,35 +29442,35 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
@@ -29482,35 +29482,35 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E714" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -29522,35 +29522,35 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E715" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -29562,35 +29562,35 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
@@ -29602,35 +29602,35 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E717" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -29642,35 +29642,35 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E718" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -29682,35 +29682,35 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E719" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -29722,35 +29722,35 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E720" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -29762,35 +29762,35 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E721" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -29802,12 +29802,12 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -29821,11 +29821,11 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -29842,12 +29842,12 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -29861,11 +29861,11 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -29882,12 +29882,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -29901,11 +29901,11 @@
         </is>
       </c>
       <c r="E724" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -29922,12 +29922,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -29941,11 +29941,11 @@
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -29962,12 +29962,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -29981,11 +29981,11 @@
         </is>
       </c>
       <c r="E726" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -30002,12 +30002,12 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -30021,11 +30021,11 @@
         </is>
       </c>
       <c r="E727" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -30042,12 +30042,12 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -30061,11 +30061,11 @@
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -30082,12 +30082,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -30101,11 +30101,11 @@
         </is>
       </c>
       <c r="E729" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -30122,12 +30122,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -30141,11 +30141,11 @@
         </is>
       </c>
       <c r="E730" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -30162,12 +30162,12 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -30181,11 +30181,11 @@
         </is>
       </c>
       <c r="E731" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -30202,12 +30202,12 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -30221,11 +30221,11 @@
         </is>
       </c>
       <c r="E732" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -30242,12 +30242,12 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -30261,11 +30261,11 @@
         </is>
       </c>
       <c r="E733" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -30282,12 +30282,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -30301,11 +30301,11 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -30322,12 +30322,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -30341,11 +30341,11 @@
         </is>
       </c>
       <c r="E735" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -30362,12 +30362,12 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -30381,11 +30381,11 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -30402,12 +30402,12 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -30421,11 +30421,11 @@
         </is>
       </c>
       <c r="E737" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -30442,12 +30442,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -30461,11 +30461,11 @@
         </is>
       </c>
       <c r="E738" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -30482,12 +30482,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -30501,11 +30501,11 @@
         </is>
       </c>
       <c r="E739" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -30522,12 +30522,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -30541,11 +30541,11 @@
         </is>
       </c>
       <c r="E740" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -30562,12 +30562,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -30581,11 +30581,11 @@
         </is>
       </c>
       <c r="E741" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -30602,12 +30602,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -30621,11 +30621,11 @@
         </is>
       </c>
       <c r="E742" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -30642,12 +30642,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -30661,11 +30661,11 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -30682,12 +30682,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -30701,11 +30701,11 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -30722,12 +30722,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -30741,11 +30741,11 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -30762,35 +30762,35 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -30802,35 +30802,35 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -30842,35 +30842,35 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -30882,35 +30882,35 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -30922,35 +30922,35 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -30962,35 +30962,35 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -31002,35 +31002,35 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -31042,35 +31042,35 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -31082,35 +31082,35 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -31122,35 +31122,35 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E755" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -31162,35 +31162,35 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -31202,35 +31202,35 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E757" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -31242,12 +31242,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -31261,11 +31261,11 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -31282,12 +31282,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -31301,11 +31301,11 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -31322,12 +31322,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -31341,11 +31341,11 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -31362,12 +31362,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -31381,11 +31381,11 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -31402,12 +31402,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -31421,11 +31421,11 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -31442,12 +31442,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -31461,11 +31461,11 @@
         </is>
       </c>
       <c r="E763" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -31482,12 +31482,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -31501,11 +31501,11 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -31522,12 +31522,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -31541,11 +31541,11 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -31562,12 +31562,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -31581,11 +31581,11 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -31602,12 +31602,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -31621,11 +31621,11 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -31642,12 +31642,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -31661,11 +31661,11 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -31682,12 +31682,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -31701,11 +31701,11 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -31722,12 +31722,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -31741,11 +31741,11 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -31762,12 +31762,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -31781,11 +31781,11 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -31802,12 +31802,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -31821,11 +31821,11 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -31842,12 +31842,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -31861,11 +31861,11 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -31882,12 +31882,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -31901,11 +31901,11 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -31922,12 +31922,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -31941,11 +31941,11 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -31962,12 +31962,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -31981,11 +31981,11 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -32002,12 +32002,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -32021,11 +32021,11 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
@@ -32042,12 +32042,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -32061,11 +32061,11 @@
         </is>
       </c>
       <c r="E778" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -32082,12 +32082,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -32101,11 +32101,11 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -32122,12 +32122,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -32141,11 +32141,11 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -32162,38 +32162,998 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B781" t="inlineStr">
+      <c r="B782" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C781" t="inlineStr">
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>576</v>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>579</v>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>71</v>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D781" t="inlineStr">
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>55</v>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E781" t="n">
+      <c r="E805" t="n">
         <v>82.3</v>
       </c>
-      <c r="F781" t="inlineStr">
+      <c r="F805" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G781" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H781" t="inlineStr">
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -32210,7 +33170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -32887,100 +33847,125 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>27 September 2026</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>91.44</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>83.3</v>
+        <v>87.2</v>
       </c>
       <c r="D27" t="n">
-        <v>87.06999999999999</v>
+        <v>90.86</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F27" t="n">
-        <v>84.88</v>
+        <v>85.69</v>
       </c>
       <c r="G27" t="n">
-        <v>92.2</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C28" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D28" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F28" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G28" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C29" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D29" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G29" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C30" t="n">
+        <v>82</v>
+      </c>
+      <c r="D30" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>68</v>
+      </c>
+      <c r="F30" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G30" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B31" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C31" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D31" t="n">
         <v>85.34</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>55</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F31" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G31" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -32995,7 +33980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -33605,114 +34590,133 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>423540</v>
+        <v>406907</v>
       </c>
       <c r="C32" t="n">
-        <v>2852</v>
+        <v>2766</v>
       </c>
       <c r="D32" t="n">
-        <v>122185</v>
+        <v>110638</v>
       </c>
       <c r="E32" t="n">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C33" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D33" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E33" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C34" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D34" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E34" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C35" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D35" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E35" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C36" t="n">
         <v>2778</v>
       </c>
       <c r="D36" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E36" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D37" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E37" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B38" t="n">
         <v>389862</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>2676</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>110408</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>579</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.64</v>
+        <v>92.87</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.15000000000001</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.98</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="17">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>76.92</v>
+        <v>78.20999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.45999999999999</v>
+        <v>94.28</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>81.95</v>
+        <v>82.06</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85.64</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.23</v>
+        <v>61.79</v>
       </c>
     </row>
     <row r="25">
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H805"/>
+  <dimension ref="A1:H817"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28362,35 +28362,35 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E686" t="n">
-        <v>5685</v>
+        <v>91.95</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>91.95%</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
@@ -28402,35 +28402,35 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E687" t="n">
-        <v>838364</v>
+        <v>88.92</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>88.92%</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -28442,35 +28442,35 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E688" t="n">
-        <v>414824</v>
+        <v>82.44</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>82.44%</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -28482,35 +28482,35 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>2833</v>
+        <v>95</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>95.00%</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -28522,35 +28522,35 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>423540</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>95.90%</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -28562,35 +28562,35 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>2852</v>
+        <v>40</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -28602,35 +28602,35 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>1218</v>
+        <v>87.66</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>87.66%</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -28642,35 +28642,35 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E693" t="n">
-        <v>213243</v>
+        <v>83.5</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>83.50%</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -28682,35 +28682,35 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E694" t="n">
-        <v>91058</v>
+        <v>89.23</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>89.23%</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -28722,35 +28722,35 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E695" t="n">
-        <v>611</v>
+        <v>69</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>69.00%</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
@@ -28762,35 +28762,35 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E696" t="n">
-        <v>122185</v>
+        <v>81.36</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>81.36%</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -28802,35 +28802,35 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>607</v>
+        <v>72.3</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>72.30%</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -28852,25 +28852,25 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>89.66</v>
+        <v>5685</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>89.66%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
@@ -28892,25 +28892,25 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E699" t="n">
-        <v>92.28</v>
+        <v>838364</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -28932,25 +28932,25 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E700" t="n">
-        <v>77.13</v>
+        <v>414824</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -28972,25 +28972,25 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>72</v>
+        <v>2833</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -29012,25 +29012,25 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E702" t="n">
-        <v>94.3</v>
+        <v>423540</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -29052,25 +29052,25 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E703" t="n">
-        <v>41.2</v>
+        <v>2852</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -29092,25 +29092,25 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E704" t="n">
-        <v>91.44</v>
+        <v>1218</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -29132,25 +29132,25 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E705" t="n">
-        <v>83.3</v>
+        <v>213243</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -29172,25 +29172,25 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E706" t="n">
-        <v>87.06999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -29212,25 +29212,25 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>72</v>
+        <v>611</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -29252,25 +29252,25 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>84.88</v>
+        <v>122185</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -29292,25 +29292,25 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>92.2</v>
+        <v>607</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -29322,12 +29322,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -29341,11 +29341,11 @@
         </is>
       </c>
       <c r="E710" t="n">
-        <v>97.44</v>
+        <v>89.66</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -29362,12 +29362,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -29381,11 +29381,11 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>95.38</v>
+        <v>92.28</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -29402,12 +29402,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -29421,11 +29421,11 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>95.59999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -29442,12 +29442,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -29461,11 +29461,11 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -29482,12 +29482,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -29501,11 +29501,11 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>92.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -29522,12 +29522,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -29541,11 +29541,11 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -29562,12 +29562,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -29581,11 +29581,11 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -29602,12 +29602,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -29621,11 +29621,11 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -29642,12 +29642,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -29661,11 +29661,11 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -29682,12 +29682,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -29701,11 +29701,11 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -29722,12 +29722,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -29741,11 +29741,11 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -29762,12 +29762,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -29781,11 +29781,11 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -29807,30 +29807,30 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>5393</v>
+        <v>97.44</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -29847,30 +29847,30 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>766540</v>
+        <v>95.38</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -29887,30 +29887,30 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>382785</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -29927,30 +29927,30 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>2695</v>
+        <v>76</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -29967,30 +29967,30 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>383755</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -30007,30 +30007,30 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>2698</v>
+        <v>40.7</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -30047,30 +30047,30 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>1175</v>
+        <v>91.02</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -30087,30 +30087,30 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>213994</v>
+        <v>83.8</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -30127,30 +30127,30 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>105543</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -30167,30 +30167,30 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>582</v>
+        <v>49</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -30207,30 +30207,30 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>108451</v>
+        <v>78.45</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -30247,30 +30247,30 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -30282,12 +30282,12 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -30301,11 +30301,11 @@
         </is>
       </c>
       <c r="E734" t="n">
-        <v>5532</v>
+        <v>5393</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -30322,12 +30322,12 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -30341,11 +30341,11 @@
         </is>
       </c>
       <c r="E735" t="n">
-        <v>781659</v>
+        <v>766540</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -30362,12 +30362,12 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -30381,11 +30381,11 @@
         </is>
       </c>
       <c r="E736" t="n">
-        <v>389707</v>
+        <v>382785</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -30402,12 +30402,12 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -30421,11 +30421,11 @@
         </is>
       </c>
       <c r="E737" t="n">
-        <v>2753</v>
+        <v>2695</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -30442,12 +30442,12 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -30461,11 +30461,11 @@
         </is>
       </c>
       <c r="E738" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -30482,12 +30482,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -30501,11 +30501,11 @@
         </is>
       </c>
       <c r="E739" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -30522,12 +30522,12 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -30541,11 +30541,11 @@
         </is>
       </c>
       <c r="E740" t="n">
-        <v>1234</v>
+        <v>1175</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -30562,12 +30562,12 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -30581,11 +30581,11 @@
         </is>
       </c>
       <c r="E741" t="n">
-        <v>211783</v>
+        <v>213994</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -30602,12 +30602,12 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -30621,11 +30621,11 @@
         </is>
       </c>
       <c r="E742" t="n">
-        <v>90299</v>
+        <v>105543</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -30642,12 +30642,12 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -30661,11 +30661,11 @@
         </is>
       </c>
       <c r="E743" t="n">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -30682,12 +30682,12 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -30701,11 +30701,11 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -30722,12 +30722,12 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -30741,11 +30741,11 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -30762,12 +30762,12 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -30781,11 +30781,11 @@
         </is>
       </c>
       <c r="E746" t="n">
-        <v>5568</v>
+        <v>5532</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -30802,12 +30802,12 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -30821,11 +30821,11 @@
         </is>
       </c>
       <c r="E747" t="n">
-        <v>783117</v>
+        <v>781659</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -30842,12 +30842,12 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -30861,11 +30861,11 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>392017</v>
+        <v>389707</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -30882,12 +30882,12 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -30901,11 +30901,11 @@
         </is>
       </c>
       <c r="E749" t="n">
-        <v>2790</v>
+        <v>2753</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -30922,12 +30922,12 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -30941,11 +30941,11 @@
         </is>
       </c>
       <c r="E750" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -30962,12 +30962,12 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -30981,11 +30981,11 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -31002,12 +31002,12 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -31021,11 +31021,11 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>1243</v>
+        <v>1234</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -31042,12 +31042,12 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -31061,11 +31061,11 @@
         </is>
       </c>
       <c r="E753" t="n">
-        <v>217252</v>
+        <v>211783</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -31082,12 +31082,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -31101,11 +31101,11 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>97836</v>
+        <v>90299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -31122,12 +31122,12 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -31141,11 +31141,11 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -31162,12 +31162,12 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -31181,11 +31181,11 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -31202,12 +31202,12 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -31221,11 +31221,11 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -31242,12 +31242,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -31261,11 +31261,11 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>5552</v>
+        <v>5568</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -31282,12 +31282,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -31301,11 +31301,11 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>824283</v>
+        <v>783117</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -31322,12 +31322,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -31341,11 +31341,11 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>410895</v>
+        <v>392017</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -31362,12 +31362,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -31381,11 +31381,11 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>2774</v>
+        <v>2790</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -31402,12 +31402,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -31421,11 +31421,11 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -31442,12 +31442,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -31482,12 +31482,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -31501,11 +31501,11 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>1223</v>
+        <v>1243</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -31522,12 +31522,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -31541,11 +31541,11 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>206128</v>
+        <v>217252</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -31562,12 +31562,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -31581,11 +31581,11 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>89897</v>
+        <v>97836</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -31602,12 +31602,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -31621,11 +31621,11 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -31642,12 +31642,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -31661,11 +31661,11 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -31682,12 +31682,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -31701,11 +31701,11 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -31732,25 +31732,25 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>86.67</v>
+        <v>5552</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
@@ -31772,25 +31772,25 @@
       </c>
       <c r="C771" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E771" t="n">
-        <v>83.43000000000001</v>
+        <v>824283</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
@@ -31812,25 +31812,25 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E772" t="n">
-        <v>85.90000000000001</v>
+        <v>410895</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
@@ -31852,25 +31852,25 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E773" t="n">
-        <v>85</v>
+        <v>2774</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
@@ -31892,25 +31892,25 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E774" t="n">
-        <v>90.09999999999999</v>
+        <v>413388</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
@@ -31932,25 +31932,25 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E775" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -31972,25 +31972,25 @@
       </c>
       <c r="C776" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E776" t="n">
-        <v>87.38</v>
+        <v>1223</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -32012,25 +32012,25 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E777" t="n">
-        <v>82</v>
+        <v>206128</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -32052,25 +32052,25 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E778" t="n">
-        <v>85.56999999999999</v>
+        <v>89897</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
@@ -32092,25 +32092,25 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E779" t="n">
-        <v>68</v>
+        <v>620</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -32132,25 +32132,25 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E780" t="n">
-        <v>83.55</v>
+        <v>116231</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
@@ -32172,25 +32172,25 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E781" t="n">
-        <v>83.09999999999999</v>
+        <v>603</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -32202,35 +32202,35 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>5347</v>
+        <v>86.67</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -32242,35 +32242,35 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E783" t="n">
-        <v>776545</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -32282,35 +32282,35 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E784" t="n">
-        <v>386683</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -32322,35 +32322,35 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E785" t="n">
-        <v>2671</v>
+        <v>85</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -32362,35 +32362,35 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>389862</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -32402,35 +32402,35 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E787" t="n">
-        <v>2676</v>
+        <v>40</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -32442,35 +32442,35 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E788" t="n">
-        <v>1155</v>
+        <v>87.38</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -32482,35 +32482,35 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>191354</v>
+        <v>82</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -32522,35 +32522,35 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E790" t="n">
-        <v>80946</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -32562,35 +32562,35 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E791" t="n">
-        <v>576</v>
+        <v>68</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -32602,35 +32602,35 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E792" t="n">
-        <v>110408</v>
+        <v>83.55</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -32642,35 +32642,35 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E793" t="n">
-        <v>579</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>83.10%</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -32692,25 +32692,25 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E794" t="n">
-        <v>97.75</v>
+        <v>5347</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>5,347</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H794" t="inlineStr">
@@ -32732,25 +32732,25 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E795" t="n">
-        <v>89.15000000000001</v>
+        <v>776545</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>7,76,545</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -32772,25 +32772,25 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E796" t="n">
-        <v>77.83</v>
+        <v>386683</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>3,86,683</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
@@ -32812,25 +32812,25 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E797" t="n">
-        <v>71</v>
+        <v>2671</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>2,671</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
@@ -32852,25 +32852,25 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E798" t="n">
-        <v>94.3</v>
+        <v>389862</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>3,89,862</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H798" t="inlineStr">
@@ -32892,25 +32892,25 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E799" t="n">
-        <v>42.9</v>
+        <v>2676</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>2,676</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H799" t="inlineStr">
@@ -32932,25 +32932,25 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E800" t="n">
-        <v>86.84999999999999</v>
+        <v>1155</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>1,155</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H800" t="inlineStr">
@@ -32972,25 +32972,25 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D801" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E801" t="n">
-        <v>81.40000000000001</v>
+        <v>191354</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>1,91,354</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H801" t="inlineStr">
@@ -33012,25 +33012,25 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D802" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E802" t="n">
-        <v>85.34</v>
+        <v>80946</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>80,946</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -33052,25 +33052,25 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E803" t="n">
-        <v>55</v>
+        <v>576</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>576</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H803" t="inlineStr">
@@ -33092,25 +33092,25 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E804" t="n">
-        <v>81.51000000000001</v>
+        <v>110408</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>1,10,408</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -33132,28 +33132,508 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>579</v>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>71</v>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D805" t="inlineStr">
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>55</v>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E805" t="n">
+      <c r="E817" t="n">
         <v>82.3</v>
       </c>
-      <c r="F805" t="inlineStr">
+      <c r="F817" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G805" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H805" t="inlineStr">
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -33170,7 +33650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -33872,100 +34352,125 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>28 September 2026</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>91.44</v>
+        <v>87.66</v>
       </c>
       <c r="C28" t="n">
-        <v>83.3</v>
+        <v>83.5</v>
       </c>
       <c r="D28" t="n">
-        <v>87.06999999999999</v>
+        <v>89.23</v>
       </c>
       <c r="E28" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F28" t="n">
-        <v>84.88</v>
+        <v>81.36</v>
       </c>
       <c r="G28" t="n">
-        <v>92.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C29" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D29" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F29" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G29" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C30" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D30" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G30" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C31" t="n">
+        <v>82</v>
+      </c>
+      <c r="D31" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>68</v>
+      </c>
+      <c r="F31" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G31" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B32" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C32" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D32" t="n">
         <v>85.34</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E32" t="n">
         <v>55</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F32" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>82.3</v>
       </c>
     </row>

--- a/aviation.xlsx
+++ b/aviation.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2747.2</v>
+        <v>2741.12</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>398077.33</v>
+        <v>396855.25</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2745.93</v>
+        <v>2739.56</v>
       </c>
     </row>
     <row r="5">
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>397576.13</v>
+        <v>396309.44</v>
       </c>
     </row>
     <row r="6">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5493.13</v>
+        <v>5480.69</v>
       </c>
     </row>
     <row r="7">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>795653.47</v>
+        <v>793164.6899999999</v>
       </c>
     </row>
     <row r="8">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>602.73</v>
+        <v>600.8099999999999</v>
       </c>
     </row>
     <row r="9">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>113945.8</v>
+        <v>113423</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>607.2</v>
+        <v>605.1900000000001</v>
       </c>
     </row>
     <row r="11">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>90759</v>
+        <v>90756.5</v>
       </c>
     </row>
     <row r="12">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1209.93</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="13">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>204704.8</v>
+        <v>204179.5</v>
       </c>
     </row>
     <row r="14">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>92.87</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88.2</v>
+        <v>88.20999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.99</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="17">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>82.45999999999999</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="18">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78.20999999999999</v>
+        <v>78.33</v>
       </c>
     </row>
     <row r="19">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>94.28</v>
+        <v>93.97</v>
       </c>
     </row>
     <row r="20">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81.37</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="21">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>82.06</v>
+        <v>82.12</v>
       </c>
     </row>
     <row r="22">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>82.16</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>85.90000000000001</v>
+        <v>86.03</v>
       </c>
     </row>
     <row r="24">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>61.79</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="25">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>87.64</v>
+        <v>87.61</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H817"/>
+  <dimension ref="A1:H841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28842,12 +28842,12 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -28861,11 +28861,11 @@
         </is>
       </c>
       <c r="E698" t="n">
-        <v>5685</v>
+        <v>5294</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,294</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -28882,12 +28882,12 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -28901,11 +28901,11 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>838364</v>
+        <v>755833</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>8,38,364</t>
+          <t>7,55,833</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -28922,12 +28922,12 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -28941,11 +28941,11 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>414824</v>
+        <v>377309</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>4,14,824</t>
+          <t>3,77,309</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -28962,12 +28962,12 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -28981,11 +28981,11 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>2833</v>
+        <v>2644</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2,833</t>
+          <t>2,644</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -29002,12 +29002,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -29021,11 +29021,11 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>423540</v>
+        <v>378524</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>4,23,540</t>
+          <t>3,78,524</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -29042,12 +29042,12 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -29061,11 +29061,11 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>2852</v>
+        <v>2650</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2,852</t>
+          <t>2,650</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -29082,12 +29082,12 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -29101,11 +29101,11 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1218</v>
+        <v>1147</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>1,218</t>
+          <t>1,147</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -29122,12 +29122,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -29141,11 +29141,11 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>213243</v>
+        <v>196300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2,13,243</t>
+          <t>1,96,300</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -29162,12 +29162,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -29181,11 +29181,11 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>91058</v>
+        <v>90719</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>91,058</t>
+          <t>90,719</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -29202,12 +29202,12 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -29221,11 +29221,11 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>611</v>
+        <v>575</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>575</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -29242,12 +29242,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -29261,11 +29261,11 @@
         </is>
       </c>
       <c r="E708" t="n">
-        <v>122185</v>
+        <v>105581</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>1,22,185</t>
+          <t>1,05,581</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -29282,12 +29282,12 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -29301,11 +29301,11 @@
         </is>
       </c>
       <c r="E709" t="n">
-        <v>607</v>
+        <v>572</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>572</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -29322,12 +29322,12 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -29362,12 +29362,12 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -29381,11 +29381,11 @@
         </is>
       </c>
       <c r="E711" t="n">
-        <v>92.28</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>92.28%</t>
+          <t>88.35%</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -29402,12 +29402,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -29421,11 +29421,11 @@
         </is>
       </c>
       <c r="E712" t="n">
-        <v>77.13</v>
+        <v>95.92</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>77.13%</t>
+          <t>95.92%</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -29442,12 +29442,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -29461,11 +29461,11 @@
         </is>
       </c>
       <c r="E713" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -29482,12 +29482,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -29501,11 +29501,11 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>94.20%</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -29522,12 +29522,12 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -29541,11 +29541,11 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>41.20%</t>
+          <t>50.00%</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -29562,12 +29562,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -29581,11 +29581,11 @@
         </is>
       </c>
       <c r="E716" t="n">
-        <v>91.44</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>91.44%</t>
+          <t>87.18%</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -29602,12 +29602,12 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -29621,11 +29621,11 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>83.30%</t>
+          <t>83.00%</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -29642,12 +29642,12 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -29661,11 +29661,11 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>87.06999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>87.07%</t>
+          <t>87.96%</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -29682,12 +29682,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -29701,11 +29701,11 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>72.00%</t>
+          <t>53.00%</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -29722,12 +29722,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -29741,11 +29741,11 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>84.88</v>
+        <v>78.88</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>84.88%</t>
+          <t>78.88%</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -29762,12 +29762,12 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -29781,11 +29781,11 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>92.2</v>
+        <v>85</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>92.20%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -29802,35 +29802,35 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E722" t="n">
-        <v>97.44</v>
+        <v>5685</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>97.44%</t>
+          <t>5,685</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -29842,35 +29842,35 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>95.38</v>
+        <v>838364</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>95.38%</t>
+          <t>8,38,364</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -29882,35 +29882,35 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>95.59999999999999</v>
+        <v>414824</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>95.60%</t>
+          <t>4,14,824</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -29922,35 +29922,35 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E725" t="n">
-        <v>76</v>
+        <v>2833</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>76.00%</t>
+          <t>2,833</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -29962,35 +29962,35 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E726" t="n">
-        <v>92.09999999999999</v>
+        <v>423540</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>92.10%</t>
+          <t>4,23,540</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -30002,35 +30002,35 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E727" t="n">
-        <v>40.7</v>
+        <v>2852</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>40.70%</t>
+          <t>2,852</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -30042,35 +30042,35 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E728" t="n">
-        <v>91.02</v>
+        <v>1218</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>91.02%</t>
+          <t>1,218</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -30082,35 +30082,35 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E729" t="n">
-        <v>83.8</v>
+        <v>213243</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>83.80%</t>
+          <t>2,13,243</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -30122,35 +30122,35 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E730" t="n">
-        <v>79.59999999999999</v>
+        <v>91058</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>79.60%</t>
+          <t>91,058</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -30162,35 +30162,35 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E731" t="n">
-        <v>49</v>
+        <v>611</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>49.00%</t>
+          <t>611</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -30202,35 +30202,35 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E732" t="n">
-        <v>78.45</v>
+        <v>122185</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>78.45%</t>
+          <t>1,22,185</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -30242,35 +30242,35 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E733" t="n">
-        <v>80</v>
+        <v>607</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>80.00%</t>
+          <t>607</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -30282,35 +30282,35 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E734" t="n">
-        <v>5393</v>
+        <v>89.66</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>5,393</t>
+          <t>89.66%</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -30322,35 +30322,35 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E735" t="n">
-        <v>766540</v>
+        <v>92.28</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>7,66,540</t>
+          <t>92.28%</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -30362,35 +30362,35 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E736" t="n">
-        <v>382785</v>
+        <v>77.13</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>3,82,785</t>
+          <t>77.13%</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -30402,35 +30402,35 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E737" t="n">
-        <v>2695</v>
+        <v>72</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2,695</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -30442,35 +30442,35 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E738" t="n">
-        <v>383755</v>
+        <v>94.3</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>3,83,755</t>
+          <t>94.30%</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -30482,35 +30482,35 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E739" t="n">
-        <v>2698</v>
+        <v>41.2</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2,698</t>
+          <t>41.20%</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -30522,35 +30522,35 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E740" t="n">
-        <v>1175</v>
+        <v>91.44</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>91.44%</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
@@ -30562,35 +30562,35 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E741" t="n">
-        <v>213994</v>
+        <v>83.3</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2,13,994</t>
+          <t>83.30%</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
@@ -30602,35 +30602,35 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E742" t="n">
-        <v>105543</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>1,05,543</t>
+          <t>87.07%</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -30642,35 +30642,35 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E743" t="n">
-        <v>582</v>
+        <v>72</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>72.00%</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -30682,35 +30682,35 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E744" t="n">
-        <v>108451</v>
+        <v>84.88</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>1,08,451</t>
+          <t>84.88%</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
@@ -30722,35 +30722,35 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E745" t="n">
-        <v>593</v>
+        <v>92.2</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>92.20%</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -30762,35 +30762,35 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E746" t="n">
-        <v>5532</v>
+        <v>97.44</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>5,532</t>
+          <t>97.44%</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
@@ -30802,35 +30802,35 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E747" t="n">
-        <v>781659</v>
+        <v>95.38</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>7,81,659</t>
+          <t>95.38%</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
@@ -30842,35 +30842,35 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E748" t="n">
-        <v>389707</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>3,89,707</t>
+          <t>95.60%</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
@@ -30882,35 +30882,35 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E749" t="n">
-        <v>2753</v>
+        <v>76</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>76.00%</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
@@ -30922,35 +30922,35 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>391952</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>3,91,952</t>
+          <t>92.10%</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
@@ -30962,35 +30962,35 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Domestic traffic</t>
+          <t>On Time Performance</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E751" t="n">
-        <v>2779</v>
+        <v>40.7</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>2,779</t>
+          <t>40.70%</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
@@ -31002,35 +31002,35 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Aircraft movements</t>
+          <t>AKASA AIR</t>
         </is>
       </c>
       <c r="E752" t="n">
-        <v>1234</v>
+        <v>91.02</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>1,234</t>
+          <t>91.02%</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -31042,35 +31042,35 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Airport footfalls</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>211783</v>
+        <v>83.8</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>2,11,783</t>
+          <t>83.80%</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
@@ -31082,35 +31082,35 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Arriving Pax</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="E754" t="n">
-        <v>90299</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>90,299</t>
+          <t>79.60%</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
@@ -31122,35 +31122,35 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>Arriving flights</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="E755" t="n">
-        <v>606</v>
+        <v>49</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>49.00%</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -31162,35 +31162,35 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
         <is>
-          <t>Departing Pax</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>121484</v>
+        <v>78.45</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>1,21,484</t>
+          <t>78.45%</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -31202,35 +31202,35 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>International traffic</t>
+          <t>Passenger Load Factor</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Departing flights</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="E757" t="n">
-        <v>628</v>
+        <v>80</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>80.00%</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -31242,12 +31242,12 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -31261,11 +31261,11 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>5568</v>
+        <v>5393</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>5,568</t>
+          <t>5,393</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -31282,12 +31282,12 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -31301,11 +31301,11 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>783117</v>
+        <v>766540</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>7,83,117</t>
+          <t>7,66,540</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -31322,12 +31322,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -31341,11 +31341,11 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>392017</v>
+        <v>382785</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>3,92,017</t>
+          <t>3,82,785</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -31362,12 +31362,12 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -31381,11 +31381,11 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>2790</v>
+        <v>2695</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>2,790</t>
+          <t>2,695</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -31402,12 +31402,12 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -31421,11 +31421,11 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>391100</v>
+        <v>383755</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>3,91,100</t>
+          <t>3,83,755</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -31442,12 +31442,12 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -31461,11 +31461,11 @@
         </is>
       </c>
       <c r="E763" t="n">
-        <v>2778</v>
+        <v>2698</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,698</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -31482,12 +31482,12 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -31501,11 +31501,11 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>1243</v>
+        <v>1175</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>1,243</t>
+          <t>1,175</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -31522,12 +31522,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -31541,11 +31541,11 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>217252</v>
+        <v>213994</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>2,17,252</t>
+          <t>2,13,994</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -31562,12 +31562,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -31581,11 +31581,11 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>97836</v>
+        <v>105543</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>97,836</t>
+          <t>1,05,543</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -31602,12 +31602,12 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -31621,11 +31621,11 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>582</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -31642,12 +31642,12 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -31661,11 +31661,11 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>119416</v>
+        <v>108451</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>1,19,416</t>
+          <t>1,08,451</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -31682,12 +31682,12 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -31701,11 +31701,11 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>593</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -31722,12 +31722,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -31741,11 +31741,11 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>5552</v>
+        <v>5532</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>5,552</t>
+          <t>5,532</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -31762,12 +31762,12 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -31781,11 +31781,11 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>824283</v>
+        <v>781659</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>8,24,283</t>
+          <t>7,81,659</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -31802,12 +31802,12 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -31821,11 +31821,11 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>410895</v>
+        <v>389707</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>4,10,895</t>
+          <t>3,89,707</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -31842,12 +31842,12 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -31861,11 +31861,11 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>2774</v>
+        <v>2753</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>2,774</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -31882,12 +31882,12 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -31901,11 +31901,11 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>413388</v>
+        <v>391952</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>4,13,388</t>
+          <t>3,91,952</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -31922,12 +31922,12 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -31941,11 +31941,11 @@
         </is>
       </c>
       <c r="E775" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>2,778</t>
+          <t>2,779</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -31962,12 +31962,12 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -31981,11 +31981,11 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>1223</v>
+        <v>1234</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>1,223</t>
+          <t>1,234</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -32002,12 +32002,12 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -32021,11 +32021,11 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>206128</v>
+        <v>211783</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>2,06,128</t>
+          <t>2,11,783</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
@@ -32042,12 +32042,12 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -32061,11 +32061,11 @@
         </is>
       </c>
       <c r="E778" t="n">
-        <v>89897</v>
+        <v>90299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>89,897</t>
+          <t>90,299</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -32082,12 +32082,12 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -32101,11 +32101,11 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>606</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
@@ -32122,12 +32122,12 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -32141,11 +32141,11 @@
         </is>
       </c>
       <c r="E780" t="n">
-        <v>116231</v>
+        <v>121484</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>1,16,231</t>
+          <t>1,21,484</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -32162,12 +32162,12 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -32181,11 +32181,11 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>603</v>
+        <v>628</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>628</t>
         </is>
       </c>
       <c r="G781" t="inlineStr">
@@ -32202,35 +32202,35 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E782" t="n">
-        <v>86.67</v>
+        <v>5568</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>86.67%</t>
+          <t>5,568</t>
         </is>
       </c>
       <c r="G782" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
@@ -32242,35 +32242,35 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E783" t="n">
-        <v>83.43000000000001</v>
+        <v>783117</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>83.43%</t>
+          <t>7,83,117</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
@@ -32282,35 +32282,35 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E784" t="n">
-        <v>85.90000000000001</v>
+        <v>392017</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>85.90%</t>
+          <t>3,92,017</t>
         </is>
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
@@ -32322,35 +32322,35 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E785" t="n">
-        <v>85</v>
+        <v>2790</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>85.00%</t>
+          <t>2,790</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
@@ -32362,35 +32362,35 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E786" t="n">
-        <v>90.09999999999999</v>
+        <v>391100</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>90.10%</t>
+          <t>3,91,100</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -32402,35 +32402,35 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>On Time Performance</t>
+          <t>Domestic traffic</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E787" t="n">
-        <v>40</v>
+        <v>2778</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>40.00%</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -32442,35 +32442,35 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>AKASA AIR</t>
+          <t>Aircraft movements</t>
         </is>
       </c>
       <c r="E788" t="n">
-        <v>87.38</v>
+        <v>1243</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>87.38%</t>
+          <t>1,243</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -32482,35 +32482,35 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Airport footfalls</t>
         </is>
       </c>
       <c r="E789" t="n">
-        <v>82</v>
+        <v>217252</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>82.00%</t>
+          <t>2,17,252</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -32522,35 +32522,35 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Arriving Pax</t>
         </is>
       </c>
       <c r="E790" t="n">
-        <v>85.56999999999999</v>
+        <v>97836</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>85.57%</t>
+          <t>97,836</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H790" t="inlineStr">
@@ -32562,35 +32562,35 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>Arriving flights</t>
         </is>
       </c>
       <c r="E791" t="n">
-        <v>68</v>
+        <v>633</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>68.00%</t>
+          <t>633</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
@@ -32602,35 +32602,35 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Departing Pax</t>
         </is>
       </c>
       <c r="E792" t="n">
-        <v>83.55</v>
+        <v>119416</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>83.55%</t>
+          <t>1,19,416</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -32642,35 +32642,35 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Passenger Load Factor</t>
+          <t>International traffic</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Departing flights</t>
         </is>
       </c>
       <c r="E793" t="n">
-        <v>83.09999999999999</v>
+        <v>610</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>83.10%</t>
+          <t>610</t>
         </is>
       </c>
       <c r="G793" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>count</t>
         </is>
       </c>
       <c r="H793" t="inlineStr">
@@ -32682,12 +32682,12 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
@@ -32701,11 +32701,11 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>5347</v>
+        <v>5552</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
-          <t>5,347</t>
+          <t>5,552</t>
         </is>
       </c>
       <c r="G794" t="inlineStr">
@@ -32722,12 +32722,12 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -32741,11 +32741,11 @@
         </is>
       </c>
       <c r="E795" t="n">
-        <v>776545</v>
+        <v>824283</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>7,76,545</t>
+          <t>8,24,283</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
@@ -32762,12 +32762,12 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -32781,11 +32781,11 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>386683</v>
+        <v>410895</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>3,86,683</t>
+          <t>4,10,895</t>
         </is>
       </c>
       <c r="G796" t="inlineStr">
@@ -32802,12 +32802,12 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -32821,11 +32821,11 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>2671</v>
+        <v>2774</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>2,671</t>
+          <t>2,774</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
@@ -32842,12 +32842,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -32861,11 +32861,11 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>389862</v>
+        <v>413388</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>3,89,862</t>
+          <t>4,13,388</t>
         </is>
       </c>
       <c r="G798" t="inlineStr">
@@ -32882,12 +32882,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -32901,11 +32901,11 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>2676</v>
+        <v>2778</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>2,676</t>
+          <t>2,778</t>
         </is>
       </c>
       <c r="G799" t="inlineStr">
@@ -32922,12 +32922,12 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -32941,11 +32941,11 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>1,155</t>
+          <t>1,223</t>
         </is>
       </c>
       <c r="G800" t="inlineStr">
@@ -32962,12 +32962,12 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -32981,11 +32981,11 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>191354</v>
+        <v>206128</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
-          <t>1,91,354</t>
+          <t>2,06,128</t>
         </is>
       </c>
       <c r="G801" t="inlineStr">
@@ -33002,12 +33002,12 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -33021,11 +33021,11 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>80946</v>
+        <v>89897</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>80,946</t>
+          <t>89,897</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
@@ -33042,12 +33042,12 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -33061,11 +33061,11 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>576</v>
+        <v>620</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>620</t>
         </is>
       </c>
       <c r="G803" t="inlineStr">
@@ -33082,12 +33082,12 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -33101,11 +33101,11 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>110408</v>
+        <v>116231</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>1,10,408</t>
+          <t>1,16,231</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
@@ -33122,12 +33122,12 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -33141,11 +33141,11 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>603</t>
         </is>
       </c>
       <c r="G805" t="inlineStr">
@@ -33162,12 +33162,12 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -33181,11 +33181,11 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>97.75</v>
+        <v>86.67</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>97.75%</t>
+          <t>86.67%</t>
         </is>
       </c>
       <c r="G806" t="inlineStr">
@@ -33202,12 +33202,12 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -33221,11 +33221,11 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>89.15000000000001</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>89.15%</t>
+          <t>83.43%</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
@@ -33242,12 +33242,12 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -33261,11 +33261,11 @@
         </is>
       </c>
       <c r="E808" t="n">
-        <v>77.83</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>77.83%</t>
+          <t>85.90%</t>
         </is>
       </c>
       <c r="G808" t="inlineStr">
@@ -33282,12 +33282,12 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -33301,11 +33301,11 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>71.00%</t>
+          <t>85.00%</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
@@ -33322,12 +33322,12 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -33341,11 +33341,11 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>94.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>94.30%</t>
+          <t>90.10%</t>
         </is>
       </c>
       <c r="G810" t="inlineStr">
@@ -33362,12 +33362,12 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -33381,11 +33381,11 @@
         </is>
       </c>
       <c r="E811" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>42.90%</t>
+          <t>40.00%</t>
         </is>
       </c>
       <c r="G811" t="inlineStr">
@@ -33402,12 +33402,12 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -33421,11 +33421,11 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>86.84999999999999</v>
+        <v>87.38</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>86.85%</t>
+          <t>87.38%</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
@@ -33442,12 +33442,12 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -33461,11 +33461,11 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>81.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>81.40%</t>
+          <t>82.00%</t>
         </is>
       </c>
       <c r="G813" t="inlineStr">
@@ -33482,12 +33482,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -33501,11 +33501,11 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>85.34</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>85.34%</t>
+          <t>85.57%</t>
         </is>
       </c>
       <c r="G814" t="inlineStr">
@@ -33522,12 +33522,12 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -33541,11 +33541,11 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>55.00%</t>
+          <t>68.00%</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
@@ -33562,12 +33562,12 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>8 September 2026</t>
+          <t>7 September 2026</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -33581,11 +33581,11 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>81.51000000000001</v>
+        <v>83.55</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>81.51%</t>
+          <t>83.55%</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
@@ -33602,38 +33602,998 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>83.10%</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="B817" t="inlineStr">
+      <c r="B818" t="inlineStr">
         <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="C817" t="inlineStr">
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>5347</v>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>5,347</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>776545</v>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>7,76,545</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>386683</v>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>3,86,683</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>2,671</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>389862</v>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>3,89,862</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Domestic traffic</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>2,676</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Aircraft movements</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>1155</v>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>1,155</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Airport footfalls</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>191354</v>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>1,91,354</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Arriving Pax</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>80946</v>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>80,946</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Arriving flights</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>576</v>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Departing Pax</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>110408</v>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>1,10,408</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>International traffic</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Departing flights</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>579</v>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>97.75%</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E831" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>89.15%</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E832" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>77.83%</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E833" t="n">
+        <v>71</v>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>71.00%</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E834" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>94.30%</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>On Time Performance</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>SpiceJet</t>
+        </is>
+      </c>
+      <c r="E835" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>42.90%</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
         <is>
           <t>Passenger Load Factor</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr">
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>AKASA AIR</t>
+        </is>
+      </c>
+      <c r="E836" t="n">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>86.85%</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Air India</t>
+        </is>
+      </c>
+      <c r="E837" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>81.40%</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="E838" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>85.34%</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Alliance Air</t>
+        </is>
+      </c>
+      <c r="E839" t="n">
+        <v>55</v>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>55.00%</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="E840" t="n">
+        <v>81.51000000000001</v>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>81.51%</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>civilaviation.gov.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>8 September 2026</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Passenger Load Factor</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
         <is>
           <t>SpiceJet</t>
         </is>
       </c>
-      <c r="E817" t="n">
+      <c r="E841" t="n">
         <v>82.3</v>
       </c>
-      <c r="F817" t="inlineStr">
+      <c r="F841" t="inlineStr">
         <is>
           <t>82.30%</t>
         </is>
       </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-      <c r="H817" t="inlineStr">
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
         <is>
           <t>civilaviation.gov.in</t>
         </is>
@@ -33650,7 +34610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -34377,100 +35337,125 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>91.44</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="D29" t="n">
-        <v>87.06999999999999</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="F29" t="n">
-        <v>84.88</v>
+        <v>78.88</v>
       </c>
       <c r="G29" t="n">
-        <v>92.2</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>91.02</v>
+        <v>91.44</v>
       </c>
       <c r="C30" t="n">
-        <v>83.8</v>
+        <v>83.3</v>
       </c>
       <c r="D30" t="n">
-        <v>79.59999999999999</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="F30" t="n">
-        <v>78.45</v>
+        <v>84.88</v>
       </c>
       <c r="G30" t="n">
-        <v>80</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>30 July 2026</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>87.38</v>
+        <v>91.02</v>
       </c>
       <c r="C31" t="n">
-        <v>82</v>
+        <v>83.8</v>
       </c>
       <c r="D31" t="n">
-        <v>85.56999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>83.55</v>
+        <v>78.45</v>
       </c>
       <c r="G31" t="n">
-        <v>83.09999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="C32" t="n">
+        <v>82</v>
+      </c>
+      <c r="D32" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="E32" t="n">
+        <v>68</v>
+      </c>
+      <c r="F32" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="G32" t="n">
+        <v>83.09999999999999</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B33" t="n">
         <v>86.84999999999999</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C33" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D33" t="n">
         <v>85.34</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E33" t="n">
         <v>55</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>81.51000000000001</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>82.3</v>
       </c>
     </row>
@@ -34485,7 +35470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -35114,114 +36099,133 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>30 August 2026</t>
+          <t>29 September 2026</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>423540</v>
+        <v>378524</v>
       </c>
       <c r="C33" t="n">
-        <v>2852</v>
+        <v>2650</v>
       </c>
       <c r="D33" t="n">
-        <v>122185</v>
+        <v>105581</v>
       </c>
       <c r="E33" t="n">
-        <v>607</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>31 July 2026</t>
+          <t>30 August 2026</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>383755</v>
+        <v>423540</v>
       </c>
       <c r="C34" t="n">
-        <v>2698</v>
+        <v>2852</v>
       </c>
       <c r="D34" t="n">
-        <v>108451</v>
+        <v>122185</v>
       </c>
       <c r="E34" t="n">
-        <v>593</v>
+        <v>607</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>31 July 2026</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>391952</v>
+        <v>383755</v>
       </c>
       <c r="C35" t="n">
-        <v>2779</v>
+        <v>2698</v>
       </c>
       <c r="D35" t="n">
-        <v>121484</v>
+        <v>108451</v>
       </c>
       <c r="E35" t="n">
-        <v>628</v>
+        <v>593</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5 September 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>391100</v>
+        <v>391952</v>
       </c>
       <c r="C36" t="n">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="D36" t="n">
-        <v>119416</v>
+        <v>121484</v>
       </c>
       <c r="E36" t="n">
-        <v>610</v>
+        <v>628</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>7 September 2026</t>
+          <t>5 September 2026</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>413388</v>
+        <v>391100</v>
       </c>
       <c r="C37" t="n">
         <v>2778</v>
       </c>
       <c r="D37" t="n">
-        <v>116231</v>
+        <v>119416</v>
       </c>
       <c r="E37" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>7 September 2026</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>413388</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2778</v>
+      </c>
+      <c r="D38" t="n">
+        <v>116231</v>
+      </c>
+      <c r="E38" t="n">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>8 September 2026</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B39" t="n">
         <v>389862</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C39" t="n">
         <v>2676</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>110408</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E39" t="n">
         <v>579</v>
       </c>
     </row>
